--- a/artfynd/A 31322-2024 artfynd.xlsx
+++ b/artfynd/A 31322-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY95"/>
+  <dimension ref="A1:AY94"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6497,7 +6497,7 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>105162655</v>
+        <v>106564418</v>
       </c>
       <c r="B52" t="n">
         <v>78569</v>
@@ -6531,19 +6531,22 @@
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
+      <c r="J52" t="inlineStr"/>
+      <c r="K52" t="inlineStr"/>
+      <c r="N52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Norrtannflo värdetrakt, Ång</t>
+          <t>Blåbärshällarna, Ång</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>598668.0395446195</v>
+        <v>598668.0119067493</v>
       </c>
       <c r="R52" t="n">
-        <v>7034492.480142549</v>
+        <v>7034493.375391286</v>
       </c>
       <c r="S52" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -6567,7 +6570,7 @@
       </c>
       <c r="Y52" t="inlineStr">
         <is>
-          <t>2022-09-21</t>
+          <t>2023-02-09</t>
         </is>
       </c>
       <c r="Z52" t="inlineStr">
@@ -6577,7 +6580,7 @@
       </c>
       <c r="AA52" t="inlineStr">
         <is>
-          <t>2022-09-21</t>
+          <t>2023-02-09</t>
         </is>
       </c>
       <c r="AB52" t="inlineStr">
@@ -6591,25 +6594,37 @@
       <c r="AE52" t="b">
         <v>0</v>
       </c>
+      <c r="AF52" t="inlineStr"/>
       <c r="AG52" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ52" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AK52" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AO52" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
       </c>
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Jennifer C. Johansson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Amanda Tas, Erland Lindblad, Steve Daurer</t>
-        </is>
-      </c>
-      <c r="AY52" t="inlineStr">
-        <is>
-          <t>Naturvärdesinventering Y-län</t>
-        </is>
-      </c>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -6845,10 +6860,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>106564418</v>
+        <v>119278582</v>
       </c>
       <c r="B55" t="n">
-        <v>78569</v>
+        <v>90562</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6861,37 +6876,34 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
-      <c r="J55" t="inlineStr"/>
-      <c r="K55" t="inlineStr"/>
-      <c r="N55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Blåbärshällarna, Ång</t>
+          <t>Storstenbäcken, Storstenbäcken, Ång</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>598668.0119067493</v>
+        <v>598478</v>
       </c>
       <c r="R55" t="n">
-        <v>7034493.375391286</v>
+        <v>7034333</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6918,22 +6930,12 @@
       </c>
       <c r="Y55" t="inlineStr">
         <is>
-          <t>2023-02-09</t>
-        </is>
-      </c>
-      <c r="Z55" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-08-22</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
         <is>
-          <t>2023-02-09</t>
-        </is>
-      </c>
-      <c r="AB55" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-08-22</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6942,44 +6944,28 @@
       <c r="AE55" t="b">
         <v>0</v>
       </c>
-      <c r="AF55" t="inlineStr"/>
       <c r="AG55" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ55" t="inlineStr">
-        <is>
-          <t>asp</t>
-        </is>
-      </c>
-      <c r="AK55" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
-      <c r="AO55" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
       </c>
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>119278582</v>
+        <v>119278693</v>
       </c>
       <c r="B56" t="n">
-        <v>90562</v>
+        <v>90846</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -6992,21 +6978,21 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -7016,10 +7002,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>598478</v>
+        <v>598485</v>
       </c>
       <c r="R56" t="n">
-        <v>7034333</v>
+        <v>7034362</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -7078,10 +7064,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>119278693</v>
+        <v>119280121</v>
       </c>
       <c r="B57" t="n">
-        <v>90846</v>
+        <v>58166</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -7090,25 +7076,25 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>658</v>
+        <v>208249</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Vanlig groda</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Rana temporaria</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -7118,10 +7104,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>598485</v>
+        <v>598391</v>
       </c>
       <c r="R57" t="n">
-        <v>7034362</v>
+        <v>7034279</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -7151,9 +7137,19 @@
           <t>2024-08-22</t>
         </is>
       </c>
+      <c r="Z57" t="inlineStr">
+        <is>
+          <t>16:47</t>
+        </is>
+      </c>
       <c r="AA57" t="inlineStr">
         <is>
           <t>2024-08-22</t>
+        </is>
+      </c>
+      <c r="AB57" t="inlineStr">
+        <is>
+          <t>16:47</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -7168,22 +7164,22 @@
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>119280121</v>
+        <v>119278842</v>
       </c>
       <c r="B58" t="n">
-        <v>58166</v>
+        <v>78526</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -7192,25 +7188,25 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>208249</v>
+        <v>6425</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Vanlig groda</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Rana temporaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -7220,13 +7216,13 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>598391</v>
+        <v>598487</v>
       </c>
       <c r="R58" t="n">
-        <v>7034279</v>
+        <v>7034370</v>
       </c>
       <c r="S58" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>
@@ -7253,19 +7249,9 @@
           <t>2024-08-22</t>
         </is>
       </c>
-      <c r="Z58" t="inlineStr">
-        <is>
-          <t>16:47</t>
-        </is>
-      </c>
       <c r="AA58" t="inlineStr">
         <is>
           <t>2024-08-22</t>
-        </is>
-      </c>
-      <c r="AB58" t="inlineStr">
-        <is>
-          <t>16:47</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -7280,22 +7266,22 @@
       <c r="AT58" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>119278842</v>
+        <v>119279180</v>
       </c>
       <c r="B59" t="n">
-        <v>78526</v>
+        <v>90562</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -7308,21 +7294,21 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -7332,13 +7318,13 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>598487</v>
+        <v>598834</v>
       </c>
       <c r="R59" t="n">
-        <v>7034370</v>
+        <v>7034566</v>
       </c>
       <c r="S59" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T59" t="inlineStr">
         <is>
@@ -7365,9 +7351,19 @@
           <t>2024-08-22</t>
         </is>
       </c>
+      <c r="Z59" t="inlineStr">
+        <is>
+          <t>16:01</t>
+        </is>
+      </c>
       <c r="AA59" t="inlineStr">
         <is>
           <t>2024-08-22</t>
+        </is>
+      </c>
+      <c r="AB59" t="inlineStr">
+        <is>
+          <t>16:01</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -7382,22 +7378,22 @@
       <c r="AT59" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>119279180</v>
+        <v>119280133</v>
       </c>
       <c r="B60" t="n">
-        <v>90562</v>
+        <v>90846</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -7410,21 +7406,21 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -7434,10 +7430,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>598834</v>
+        <v>598369</v>
       </c>
       <c r="R60" t="n">
-        <v>7034566</v>
+        <v>7034251</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -7467,19 +7463,9 @@
           <t>2024-08-22</t>
         </is>
       </c>
-      <c r="Z60" t="inlineStr">
-        <is>
-          <t>16:01</t>
-        </is>
-      </c>
       <c r="AA60" t="inlineStr">
         <is>
           <t>2024-08-22</t>
-        </is>
-      </c>
-      <c r="AB60" t="inlineStr">
-        <is>
-          <t>16:01</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7494,19 +7480,19 @@
       <c r="AT60" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX60" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>119280133</v>
+        <v>119277952</v>
       </c>
       <c r="B61" t="n">
         <v>90846</v>
@@ -7546,13 +7532,13 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>598369</v>
+        <v>598330</v>
       </c>
       <c r="R61" t="n">
-        <v>7034251</v>
+        <v>7034204</v>
       </c>
       <c r="S61" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T61" t="inlineStr">
         <is>
@@ -7608,10 +7594,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>119277952</v>
+        <v>119278908</v>
       </c>
       <c r="B62" t="n">
-        <v>90846</v>
+        <v>57463</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -7624,37 +7610,46 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>658</v>
+        <v>103021</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
-        </is>
-      </c>
-      <c r="I62" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M62" t="inlineStr">
+        <is>
+          <t>stationär</t>
+        </is>
+      </c>
       <c r="P62" t="inlineStr">
         <is>
           <t>Storstenbäcken, Storstenbäcken, Ång</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>598330</v>
+        <v>598683</v>
       </c>
       <c r="R62" t="n">
-        <v>7034204</v>
+        <v>7034343</v>
       </c>
       <c r="S62" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T62" t="inlineStr">
         <is>
@@ -7681,9 +7676,19 @@
           <t>2024-08-22</t>
         </is>
       </c>
+      <c r="Z62" t="inlineStr">
+        <is>
+          <t>15:36</t>
+        </is>
+      </c>
       <c r="AA62" t="inlineStr">
         <is>
           <t>2024-08-22</t>
+        </is>
+      </c>
+      <c r="AB62" t="inlineStr">
+        <is>
+          <t>15:36</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7698,22 +7703,22 @@
       <c r="AT62" t="inlineStr"/>
       <c r="AW62" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX62" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>119278908</v>
+        <v>119279008</v>
       </c>
       <c r="B63" t="n">
-        <v>57463</v>
+        <v>57310</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -7726,43 +7731,34 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I63" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="M63" t="inlineStr">
-        <is>
-          <t>stationär</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
           <t>Storstenbäcken, Storstenbäcken, Ång</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>598683</v>
+        <v>598744</v>
       </c>
       <c r="R63" t="n">
-        <v>7034343</v>
+        <v>7034453</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7794,7 +7790,7 @@
       </c>
       <c r="Z63" t="inlineStr">
         <is>
-          <t>15:36</t>
+          <t>15:48</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
@@ -7804,7 +7800,12 @@
       </c>
       <c r="AB63" t="inlineStr">
         <is>
-          <t>15:36</t>
+          <t>15:48</t>
+        </is>
+      </c>
+      <c r="AC63" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7831,7 +7832,7 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>119279008</v>
+        <v>119280145</v>
       </c>
       <c r="B64" t="n">
         <v>57310</v>
@@ -7871,10 +7872,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>598744</v>
+        <v>598349</v>
       </c>
       <c r="R64" t="n">
-        <v>7034453</v>
+        <v>7034259</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7906,7 +7907,7 @@
       </c>
       <c r="Z64" t="inlineStr">
         <is>
-          <t>15:48</t>
+          <t>16:52</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
@@ -7916,7 +7917,7 @@
       </c>
       <c r="AB64" t="inlineStr">
         <is>
-          <t>15:48</t>
+          <t>16:52</t>
         </is>
       </c>
       <c r="AC64" t="inlineStr">
@@ -7948,10 +7949,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>119280145</v>
+        <v>119280135</v>
       </c>
       <c r="B65" t="n">
-        <v>57310</v>
+        <v>90562</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -7964,21 +7965,21 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -7988,10 +7989,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>598349</v>
+        <v>598365</v>
       </c>
       <c r="R65" t="n">
-        <v>7034259</v>
+        <v>7034248</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -8021,24 +8022,9 @@
           <t>2024-08-22</t>
         </is>
       </c>
-      <c r="Z65" t="inlineStr">
-        <is>
-          <t>16:52</t>
-        </is>
-      </c>
       <c r="AA65" t="inlineStr">
         <is>
           <t>2024-08-22</t>
-        </is>
-      </c>
-      <c r="AB65" t="inlineStr">
-        <is>
-          <t>16:52</t>
-        </is>
-      </c>
-      <c r="AC65" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -8053,22 +8039,22 @@
       <c r="AT65" t="inlineStr"/>
       <c r="AW65" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX65" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>119280135</v>
+        <v>119279051</v>
       </c>
       <c r="B66" t="n">
-        <v>90562</v>
+        <v>90582</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -8081,21 +8067,21 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>1202</v>
+        <v>5442</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -8105,10 +8091,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>598365</v>
+        <v>598610</v>
       </c>
       <c r="R66" t="n">
-        <v>7034248</v>
+        <v>7034505</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -8167,10 +8153,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>119279051</v>
+        <v>119279649</v>
       </c>
       <c r="B67" t="n">
-        <v>90582</v>
+        <v>57310</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -8183,21 +8169,21 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>5442</v>
+        <v>100109</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -8207,10 +8193,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>598610</v>
+        <v>598612</v>
       </c>
       <c r="R67" t="n">
-        <v>7034505</v>
+        <v>7034546</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -8240,9 +8226,24 @@
           <t>2024-08-22</t>
         </is>
       </c>
+      <c r="Z67" t="inlineStr">
+        <is>
+          <t>16:26</t>
+        </is>
+      </c>
       <c r="AA67" t="inlineStr">
         <is>
           <t>2024-08-22</t>
+        </is>
+      </c>
+      <c r="AB67" t="inlineStr">
+        <is>
+          <t>16:26</t>
+        </is>
+      </c>
+      <c r="AC67" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -8257,22 +8258,22 @@
       <c r="AT67" t="inlineStr"/>
       <c r="AW67" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX67" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>119279649</v>
+        <v>119278756</v>
       </c>
       <c r="B68" t="n">
-        <v>57310</v>
+        <v>90846</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -8285,21 +8286,21 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>100109</v>
+        <v>658</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -8309,10 +8310,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>598612</v>
+        <v>598485</v>
       </c>
       <c r="R68" t="n">
-        <v>7034546</v>
+        <v>7034367</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -8342,24 +8343,9 @@
           <t>2024-08-22</t>
         </is>
       </c>
-      <c r="Z68" t="inlineStr">
-        <is>
-          <t>16:26</t>
-        </is>
-      </c>
       <c r="AA68" t="inlineStr">
         <is>
           <t>2024-08-22</t>
-        </is>
-      </c>
-      <c r="AB68" t="inlineStr">
-        <is>
-          <t>16:26</t>
-        </is>
-      </c>
-      <c r="AC68" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -8374,19 +8360,19 @@
       <c r="AT68" t="inlineStr"/>
       <c r="AW68" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX68" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>119278756</v>
+        <v>119278599</v>
       </c>
       <c r="B69" t="n">
         <v>90846</v>
@@ -8426,10 +8412,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>598485</v>
+        <v>598483</v>
       </c>
       <c r="R69" t="n">
-        <v>7034367</v>
+        <v>7034339</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -8488,7 +8474,7 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>119278599</v>
+        <v>119278432</v>
       </c>
       <c r="B70" t="n">
         <v>90846</v>
@@ -8528,13 +8514,13 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>598483</v>
+        <v>598410</v>
       </c>
       <c r="R70" t="n">
-        <v>7034339</v>
+        <v>7034317</v>
       </c>
       <c r="S70" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T70" t="inlineStr">
         <is>
@@ -8590,10 +8576,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>119278432</v>
+        <v>119278224</v>
       </c>
       <c r="B71" t="n">
-        <v>90846</v>
+        <v>57310</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
@@ -8606,37 +8592,42 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>658</v>
+        <v>100109</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
+      <c r="M71" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P71" t="inlineStr">
         <is>
           <t>Storstenbäcken, Storstenbäcken, Ång</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>598410</v>
+        <v>598498</v>
       </c>
       <c r="R71" t="n">
-        <v>7034317</v>
+        <v>7034222</v>
       </c>
       <c r="S71" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T71" t="inlineStr">
         <is>
@@ -8663,9 +8654,19 @@
           <t>2024-08-22</t>
         </is>
       </c>
+      <c r="Z71" t="inlineStr">
+        <is>
+          <t>14:58</t>
+        </is>
+      </c>
       <c r="AA71" t="inlineStr">
         <is>
           <t>2024-08-22</t>
+        </is>
+      </c>
+      <c r="AB71" t="inlineStr">
+        <is>
+          <t>14:58</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -8680,22 +8681,22 @@
       <c r="AT71" t="inlineStr"/>
       <c r="AW71" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX71" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>119278224</v>
+        <v>119278487</v>
       </c>
       <c r="B72" t="n">
-        <v>57310</v>
+        <v>90846</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
@@ -8708,39 +8709,34 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>100109</v>
+        <v>658</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
-      <c r="M72" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P72" t="inlineStr">
         <is>
           <t>Storstenbäcken, Storstenbäcken, Ång</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>598498</v>
+        <v>598580</v>
       </c>
       <c r="R72" t="n">
-        <v>7034222</v>
+        <v>7034264</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -8772,7 +8768,7 @@
       </c>
       <c r="Z72" t="inlineStr">
         <is>
-          <t>14:58</t>
+          <t>15:16</t>
         </is>
       </c>
       <c r="AA72" t="inlineStr">
@@ -8782,7 +8778,7 @@
       </c>
       <c r="AB72" t="inlineStr">
         <is>
-          <t>14:58</t>
+          <t>15:16</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -8809,10 +8805,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>119278487</v>
+        <v>119278270</v>
       </c>
       <c r="B73" t="n">
-        <v>90846</v>
+        <v>57310</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
@@ -8825,34 +8821,39 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>658</v>
+        <v>100109</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
+      <c r="M73" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P73" t="inlineStr">
         <is>
           <t>Storstenbäcken, Storstenbäcken, Ång</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>598580</v>
+        <v>598520</v>
       </c>
       <c r="R73" t="n">
-        <v>7034264</v>
+        <v>7034227</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8884,7 +8885,7 @@
       </c>
       <c r="Z73" t="inlineStr">
         <is>
-          <t>15:16</t>
+          <t>15:02</t>
         </is>
       </c>
       <c r="AA73" t="inlineStr">
@@ -8894,7 +8895,7 @@
       </c>
       <c r="AB73" t="inlineStr">
         <is>
-          <t>15:16</t>
+          <t>15:02</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -8921,10 +8922,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>119278270</v>
+        <v>119278422</v>
       </c>
       <c r="B74" t="n">
-        <v>57310</v>
+        <v>97907</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
@@ -8933,31 +8934,30 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I74" t="inlineStr"/>
-      <c r="M74" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr">
+        <is>
+          <t>50</t>
         </is>
       </c>
       <c r="P74" t="inlineStr">
@@ -8966,10 +8966,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>598520</v>
+        <v>598537</v>
       </c>
       <c r="R74" t="n">
-        <v>7034227</v>
+        <v>7034202</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -9001,7 +9001,7 @@
       </c>
       <c r="Z74" t="inlineStr">
         <is>
-          <t>15:02</t>
+          <t>15:06</t>
         </is>
       </c>
       <c r="AA74" t="inlineStr">
@@ -9011,7 +9011,7 @@
       </c>
       <c r="AB74" t="inlineStr">
         <is>
-          <t>15:02</t>
+          <t>15:06</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -9038,10 +9038,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>119278422</v>
+        <v>119279160</v>
       </c>
       <c r="B75" t="n">
-        <v>97907</v>
+        <v>90562</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
@@ -9050,42 +9050,38 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I75" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr"/>
       <c r="P75" t="inlineStr">
         <is>
           <t>Storstenbäcken, Storstenbäcken, Ång</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>598537</v>
+        <v>598621</v>
       </c>
       <c r="R75" t="n">
-        <v>7034202</v>
+        <v>7034555</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -9115,19 +9111,9 @@
           <t>2024-08-22</t>
         </is>
       </c>
-      <c r="Z75" t="inlineStr">
-        <is>
-          <t>15:06</t>
-        </is>
-      </c>
       <c r="AA75" t="inlineStr">
         <is>
           <t>2024-08-22</t>
-        </is>
-      </c>
-      <c r="AB75" t="inlineStr">
-        <is>
-          <t>15:06</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -9142,22 +9128,22 @@
       <c r="AT75" t="inlineStr"/>
       <c r="AW75" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX75" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>119279160</v>
+        <v>119279605</v>
       </c>
       <c r="B76" t="n">
-        <v>90562</v>
+        <v>90527</v>
       </c>
       <c r="C76" t="inlineStr">
         <is>
@@ -9166,25 +9152,25 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>1202</v>
+        <v>5447</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -9194,10 +9180,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>598621</v>
+        <v>598616</v>
       </c>
       <c r="R76" t="n">
-        <v>7034555</v>
+        <v>7034570</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -9256,10 +9242,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>119279605</v>
+        <v>119278413</v>
       </c>
       <c r="B77" t="n">
-        <v>90527</v>
+        <v>90846</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
@@ -9268,25 +9254,25 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>5447</v>
+        <v>658</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -9296,10 +9282,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>598616</v>
+        <v>598404</v>
       </c>
       <c r="R77" t="n">
-        <v>7034570</v>
+        <v>7034323</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -9358,7 +9344,7 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>119278413</v>
+        <v>119278420</v>
       </c>
       <c r="B78" t="n">
         <v>90846</v>
@@ -9398,10 +9384,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>598404</v>
+        <v>598415</v>
       </c>
       <c r="R78" t="n">
-        <v>7034323</v>
+        <v>7034330</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -9460,10 +9446,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>119278420</v>
+        <v>119279166</v>
       </c>
       <c r="B79" t="n">
-        <v>90846</v>
+        <v>56514</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
@@ -9476,34 +9462,39 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>658</v>
+        <v>102612</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
+      <c r="M79" t="inlineStr">
+        <is>
+          <t>stationär</t>
+        </is>
+      </c>
       <c r="P79" t="inlineStr">
         <is>
           <t>Storstenbäcken, Storstenbäcken, Ång</t>
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>598415</v>
+        <v>598836</v>
       </c>
       <c r="R79" t="n">
-        <v>7034330</v>
+        <v>7034550</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -9533,9 +9524,19 @@
           <t>2024-08-22</t>
         </is>
       </c>
+      <c r="Z79" t="inlineStr">
+        <is>
+          <t>16:00</t>
+        </is>
+      </c>
       <c r="AA79" t="inlineStr">
         <is>
           <t>2024-08-22</t>
+        </is>
+      </c>
+      <c r="AB79" t="inlineStr">
+        <is>
+          <t>16:00</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -9550,22 +9551,22 @@
       <c r="AT79" t="inlineStr"/>
       <c r="AW79" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX79" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>119279166</v>
+        <v>119278912</v>
       </c>
       <c r="B80" t="n">
-        <v>56514</v>
+        <v>57310</v>
       </c>
       <c r="C80" t="inlineStr">
         <is>
@@ -9578,16 +9579,16 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>102612</v>
+        <v>100109</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
@@ -9596,21 +9597,16 @@
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
-      <c r="M80" t="inlineStr">
-        <is>
-          <t>stationär</t>
-        </is>
-      </c>
       <c r="P80" t="inlineStr">
         <is>
           <t>Storstenbäcken, Storstenbäcken, Ång</t>
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>598836</v>
+        <v>598484</v>
       </c>
       <c r="R80" t="n">
-        <v>7034550</v>
+        <v>7034390</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -9640,19 +9636,14 @@
           <t>2024-08-22</t>
         </is>
       </c>
-      <c r="Z80" t="inlineStr">
-        <is>
-          <t>16:00</t>
-        </is>
-      </c>
       <c r="AA80" t="inlineStr">
         <is>
           <t>2024-08-22</t>
         </is>
       </c>
-      <c r="AB80" t="inlineStr">
-        <is>
-          <t>16:00</t>
+      <c r="AC80" t="inlineStr">
+        <is>
+          <t>Ringhack på gammal tall</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -9667,22 +9658,22 @@
       <c r="AT80" t="inlineStr"/>
       <c r="AW80" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX80" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>119278912</v>
+        <v>119279131</v>
       </c>
       <c r="B81" t="n">
-        <v>57310</v>
+        <v>90846</v>
       </c>
       <c r="C81" t="inlineStr">
         <is>
@@ -9695,21 +9686,21 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>100109</v>
+        <v>658</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
@@ -9719,13 +9710,13 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>598484</v>
+        <v>598616</v>
       </c>
       <c r="R81" t="n">
-        <v>7034390</v>
+        <v>7034552</v>
       </c>
       <c r="S81" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T81" t="inlineStr">
         <is>
@@ -9755,11 +9746,6 @@
       <c r="AA81" t="inlineStr">
         <is>
           <t>2024-08-22</t>
-        </is>
-      </c>
-      <c r="AC81" t="inlineStr">
-        <is>
-          <t>Ringhack på gammal tall</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -9786,7 +9772,7 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>119279131</v>
+        <v>119278576</v>
       </c>
       <c r="B82" t="n">
         <v>90846</v>
@@ -9826,13 +9812,13 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>598616</v>
+        <v>598475</v>
       </c>
       <c r="R82" t="n">
-        <v>7034552</v>
+        <v>7034340</v>
       </c>
       <c r="S82" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T82" t="inlineStr">
         <is>
@@ -9888,7 +9874,7 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>119278576</v>
+        <v>119278406</v>
       </c>
       <c r="B83" t="n">
         <v>90846</v>
@@ -9928,13 +9914,13 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>598475</v>
+        <v>598520</v>
       </c>
       <c r="R83" t="n">
-        <v>7034340</v>
+        <v>7034228</v>
       </c>
       <c r="S83" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T83" t="inlineStr">
         <is>
@@ -9961,9 +9947,19 @@
           <t>2024-08-22</t>
         </is>
       </c>
+      <c r="Z83" t="inlineStr">
+        <is>
+          <t>15:04</t>
+        </is>
+      </c>
       <c r="AA83" t="inlineStr">
         <is>
           <t>2024-08-22</t>
+        </is>
+      </c>
+      <c r="AB83" t="inlineStr">
+        <is>
+          <t>15:04</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -9978,19 +9974,19 @@
       <c r="AT83" t="inlineStr"/>
       <c r="AW83" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX83" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>119278406</v>
+        <v>119278466</v>
       </c>
       <c r="B84" t="n">
         <v>90846</v>
@@ -10030,10 +10026,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>598520</v>
+        <v>598446</v>
       </c>
       <c r="R84" t="n">
-        <v>7034228</v>
+        <v>7034308</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -10063,19 +10059,9 @@
           <t>2024-08-22</t>
         </is>
       </c>
-      <c r="Z84" t="inlineStr">
-        <is>
-          <t>15:04</t>
-        </is>
-      </c>
       <c r="AA84" t="inlineStr">
         <is>
           <t>2024-08-22</t>
-        </is>
-      </c>
-      <c r="AB84" t="inlineStr">
-        <is>
-          <t>15:04</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -10090,22 +10076,22 @@
       <c r="AT84" t="inlineStr"/>
       <c r="AW84" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX84" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>119278466</v>
+        <v>119278919</v>
       </c>
       <c r="B85" t="n">
-        <v>90846</v>
+        <v>57310</v>
       </c>
       <c r="C85" t="inlineStr">
         <is>
@@ -10118,34 +10104,39 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>658</v>
+        <v>100109</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
+      <c r="M85" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P85" t="inlineStr">
         <is>
           <t>Storstenbäcken, Storstenbäcken, Ång</t>
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>598446</v>
+        <v>598687</v>
       </c>
       <c r="R85" t="n">
-        <v>7034308</v>
+        <v>7034364</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -10175,9 +10166,19 @@
           <t>2024-08-22</t>
         </is>
       </c>
+      <c r="Z85" t="inlineStr">
+        <is>
+          <t>15:37</t>
+        </is>
+      </c>
       <c r="AA85" t="inlineStr">
         <is>
           <t>2024-08-22</t>
+        </is>
+      </c>
+      <c r="AB85" t="inlineStr">
+        <is>
+          <t>15:37</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -10192,22 +10193,22 @@
       <c r="AT85" t="inlineStr"/>
       <c r="AW85" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX85" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>119278919</v>
+        <v>119278212</v>
       </c>
       <c r="B86" t="n">
-        <v>57310</v>
+        <v>90752</v>
       </c>
       <c r="C86" t="inlineStr">
         <is>
@@ -10216,43 +10217,38 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>100109</v>
+        <v>48</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lappticka</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Amylocystis lapponica</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Romell) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
-      <c r="M86" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P86" t="inlineStr">
         <is>
           <t>Storstenbäcken, Storstenbäcken, Ång</t>
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>598687</v>
+        <v>598364</v>
       </c>
       <c r="R86" t="n">
-        <v>7034364</v>
+        <v>7034253</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -10282,19 +10278,9 @@
           <t>2024-08-22</t>
         </is>
       </c>
-      <c r="Z86" t="inlineStr">
-        <is>
-          <t>15:37</t>
-        </is>
-      </c>
       <c r="AA86" t="inlineStr">
         <is>
           <t>2024-08-22</t>
-        </is>
-      </c>
-      <c r="AB86" t="inlineStr">
-        <is>
-          <t>15:37</t>
         </is>
       </c>
       <c r="AD86" t="b">
@@ -10309,22 +10295,22 @@
       <c r="AT86" t="inlineStr"/>
       <c r="AW86" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX86" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>119278212</v>
+        <v>119278019</v>
       </c>
       <c r="B87" t="n">
-        <v>90752</v>
+        <v>90562</v>
       </c>
       <c r="C87" t="inlineStr">
         <is>
@@ -10333,25 +10319,25 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>48</v>
+        <v>1202</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Lappticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Amylocystis lapponica</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Romell) Bondartsev &amp; Singer</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
@@ -10361,10 +10347,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>598364</v>
+        <v>598348</v>
       </c>
       <c r="R87" t="n">
-        <v>7034253</v>
+        <v>7034205</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -10423,10 +10409,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>119278019</v>
+        <v>119278518</v>
       </c>
       <c r="B88" t="n">
-        <v>90562</v>
+        <v>90846</v>
       </c>
       <c r="C88" t="inlineStr">
         <is>
@@ -10439,21 +10425,21 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
@@ -10463,10 +10449,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>598348</v>
+        <v>598471</v>
       </c>
       <c r="R88" t="n">
-        <v>7034205</v>
+        <v>7034306</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -10525,10 +10511,10 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>119278518</v>
+        <v>119278675</v>
       </c>
       <c r="B89" t="n">
-        <v>90846</v>
+        <v>56522</v>
       </c>
       <c r="C89" t="inlineStr">
         <is>
@@ -10537,38 +10523,52 @@
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E89" t="n">
-        <v>658</v>
+        <v>100138</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
-        </is>
-      </c>
-      <c r="I89" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I89" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L89" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="M89" t="inlineStr">
+        <is>
+          <t>stationär</t>
+        </is>
+      </c>
       <c r="P89" t="inlineStr">
         <is>
           <t>Storstenbäcken, Storstenbäcken, Ång</t>
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>598471</v>
+        <v>598584</v>
       </c>
       <c r="R89" t="n">
-        <v>7034306</v>
+        <v>7034293</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -10598,9 +10598,19 @@
           <t>2024-08-22</t>
         </is>
       </c>
+      <c r="Z89" t="inlineStr">
+        <is>
+          <t>15:25</t>
+        </is>
+      </c>
       <c r="AA89" t="inlineStr">
         <is>
           <t>2024-08-22</t>
+        </is>
+      </c>
+      <c r="AB89" t="inlineStr">
+        <is>
+          <t>15:25</t>
         </is>
       </c>
       <c r="AD89" t="b">
@@ -10615,22 +10625,22 @@
       <c r="AT89" t="inlineStr"/>
       <c r="AW89" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX89" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY89" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>119278675</v>
+        <v>119278968</v>
       </c>
       <c r="B90" t="n">
-        <v>56522</v>
+        <v>57310</v>
       </c>
       <c r="C90" t="inlineStr">
         <is>
@@ -10639,52 +10649,38 @@
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E90" t="n">
-        <v>100138</v>
+        <v>100109</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I90" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="L90" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
-      <c r="M90" t="inlineStr">
-        <is>
-          <t>stationär</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I90" t="inlineStr"/>
       <c r="P90" t="inlineStr">
         <is>
           <t>Storstenbäcken, Storstenbäcken, Ång</t>
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>598584</v>
+        <v>598747</v>
       </c>
       <c r="R90" t="n">
-        <v>7034293</v>
+        <v>7034393</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -10716,7 +10712,7 @@
       </c>
       <c r="Z90" t="inlineStr">
         <is>
-          <t>15:25</t>
+          <t>15:44</t>
         </is>
       </c>
       <c r="AA90" t="inlineStr">
@@ -10726,7 +10722,12 @@
       </c>
       <c r="AB90" t="inlineStr">
         <is>
-          <t>15:25</t>
+          <t>15:44</t>
+        </is>
+      </c>
+      <c r="AC90" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD90" t="b">
@@ -10753,10 +10754,10 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>119278968</v>
+        <v>119278034</v>
       </c>
       <c r="B91" t="n">
-        <v>57310</v>
+        <v>90846</v>
       </c>
       <c r="C91" t="inlineStr">
         <is>
@@ -10769,21 +10770,21 @@
         </is>
       </c>
       <c r="E91" t="n">
-        <v>100109</v>
+        <v>658</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
@@ -10793,13 +10794,13 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>598747</v>
+        <v>598358</v>
       </c>
       <c r="R91" t="n">
-        <v>7034393</v>
+        <v>7034250</v>
       </c>
       <c r="S91" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T91" t="inlineStr">
         <is>
@@ -10826,24 +10827,9 @@
           <t>2024-08-22</t>
         </is>
       </c>
-      <c r="Z91" t="inlineStr">
-        <is>
-          <t>15:44</t>
-        </is>
-      </c>
       <c r="AA91" t="inlineStr">
         <is>
           <t>2024-08-22</t>
-        </is>
-      </c>
-      <c r="AB91" t="inlineStr">
-        <is>
-          <t>15:44</t>
-        </is>
-      </c>
-      <c r="AC91" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD91" t="b">
@@ -10858,22 +10844,22 @@
       <c r="AT91" t="inlineStr"/>
       <c r="AW91" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX91" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY91" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>119278034</v>
+        <v>119280106</v>
       </c>
       <c r="B92" t="n">
-        <v>90846</v>
+        <v>57310</v>
       </c>
       <c r="C92" t="inlineStr">
         <is>
@@ -10886,21 +10872,21 @@
         </is>
       </c>
       <c r="E92" t="n">
-        <v>658</v>
+        <v>100109</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
@@ -10910,13 +10896,13 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>598358</v>
+        <v>598406</v>
       </c>
       <c r="R92" t="n">
-        <v>7034250</v>
+        <v>7034339</v>
       </c>
       <c r="S92" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T92" t="inlineStr">
         <is>
@@ -10943,9 +10929,24 @@
           <t>2024-08-22</t>
         </is>
       </c>
+      <c r="Z92" t="inlineStr">
+        <is>
+          <t>16:44</t>
+        </is>
+      </c>
       <c r="AA92" t="inlineStr">
         <is>
           <t>2024-08-22</t>
+        </is>
+      </c>
+      <c r="AB92" t="inlineStr">
+        <is>
+          <t>16:44</t>
+        </is>
+      </c>
+      <c r="AC92" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD92" t="b">
@@ -10960,22 +10961,22 @@
       <c r="AT92" t="inlineStr"/>
       <c r="AW92" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX92" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY92" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>119280106</v>
+        <v>119279175</v>
       </c>
       <c r="B93" t="n">
-        <v>57310</v>
+        <v>57463</v>
       </c>
       <c r="C93" t="inlineStr">
         <is>
@@ -10988,37 +10989,42 @@
         </is>
       </c>
       <c r="E93" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
+      <c r="M93" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P93" t="inlineStr">
         <is>
           <t>Storstenbäcken, Storstenbäcken, Ång</t>
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>598406</v>
+        <v>598634</v>
       </c>
       <c r="R93" t="n">
-        <v>7034339</v>
+        <v>7034559</v>
       </c>
       <c r="S93" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T93" t="inlineStr">
         <is>
@@ -11045,24 +11051,9 @@
           <t>2024-08-22</t>
         </is>
       </c>
-      <c r="Z93" t="inlineStr">
-        <is>
-          <t>16:44</t>
-        </is>
-      </c>
       <c r="AA93" t="inlineStr">
         <is>
           <t>2024-08-22</t>
-        </is>
-      </c>
-      <c r="AB93" t="inlineStr">
-        <is>
-          <t>16:44</t>
-        </is>
-      </c>
-      <c r="AC93" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD93" t="b">
@@ -11077,22 +11068,22 @@
       <c r="AT93" t="inlineStr"/>
       <c r="AW93" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX93" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY93" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>119279175</v>
+        <v>119277960</v>
       </c>
       <c r="B94" t="n">
-        <v>57463</v>
+        <v>97907</v>
       </c>
       <c r="C94" t="inlineStr">
         <is>
@@ -11101,31 +11092,30 @@
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E94" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I94" t="inlineStr"/>
-      <c r="M94" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I94" t="inlineStr">
+        <is>
+          <t>20</t>
         </is>
       </c>
       <c r="P94" t="inlineStr">
@@ -11134,13 +11124,13 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>598634</v>
+        <v>598364</v>
       </c>
       <c r="R94" t="n">
-        <v>7034559</v>
+        <v>7034215</v>
       </c>
       <c r="S94" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T94" t="inlineStr">
         <is>
@@ -11167,9 +11157,19 @@
           <t>2024-08-22</t>
         </is>
       </c>
+      <c r="Z94" t="inlineStr">
+        <is>
+          <t>14:47</t>
+        </is>
+      </c>
       <c r="AA94" t="inlineStr">
         <is>
           <t>2024-08-22</t>
+        </is>
+      </c>
+      <c r="AB94" t="inlineStr">
+        <is>
+          <t>14:47</t>
         </is>
       </c>
       <c r="AD94" t="b">
@@ -11184,131 +11184,15 @@
       <c r="AT94" t="inlineStr"/>
       <c r="AW94" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX94" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY94" t="inlineStr"/>
-    </row>
-    <row r="95">
-      <c r="A95" t="n">
-        <v>119277960</v>
-      </c>
-      <c r="B95" t="n">
-        <v>97907</v>
-      </c>
-      <c r="C95" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D95" t="inlineStr">
-        <is>
-          <t>VU</t>
-        </is>
-      </c>
-      <c r="E95" t="n">
-        <v>220787</v>
-      </c>
-      <c r="F95" t="inlineStr">
-        <is>
-          <t>Knärot</t>
-        </is>
-      </c>
-      <c r="G95" t="inlineStr">
-        <is>
-          <t>Goodyera repens</t>
-        </is>
-      </c>
-      <c r="H95" t="inlineStr">
-        <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I95" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="P95" t="inlineStr">
-        <is>
-          <t>Storstenbäcken, Storstenbäcken, Ång</t>
-        </is>
-      </c>
-      <c r="Q95" t="n">
-        <v>598364</v>
-      </c>
-      <c r="R95" t="n">
-        <v>7034215</v>
-      </c>
-      <c r="S95" t="n">
-        <v>10</v>
-      </c>
-      <c r="T95" t="inlineStr">
-        <is>
-          <t>Västernorrland</t>
-        </is>
-      </c>
-      <c r="U95" t="inlineStr">
-        <is>
-          <t>Sollefteå</t>
-        </is>
-      </c>
-      <c r="V95" t="inlineStr">
-        <is>
-          <t>Ångermanland</t>
-        </is>
-      </c>
-      <c r="W95" t="inlineStr">
-        <is>
-          <t>Ådals-Liden</t>
-        </is>
-      </c>
-      <c r="Y95" t="inlineStr">
-        <is>
-          <t>2024-08-22</t>
-        </is>
-      </c>
-      <c r="Z95" t="inlineStr">
-        <is>
-          <t>14:47</t>
-        </is>
-      </c>
-      <c r="AA95" t="inlineStr">
-        <is>
-          <t>2024-08-22</t>
-        </is>
-      </c>
-      <c r="AB95" t="inlineStr">
-        <is>
-          <t>14:47</t>
-        </is>
-      </c>
-      <c r="AD95" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE95" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG95" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT95" t="inlineStr"/>
-      <c r="AW95" t="inlineStr">
-        <is>
-          <t>Kim Hultgren</t>
-        </is>
-      </c>
-      <c r="AX95" t="inlineStr">
-        <is>
-          <t>Kim Hultgren</t>
-        </is>
-      </c>
-      <c r="AY95" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 31322-2024 artfynd.xlsx
+++ b/artfynd/A 31322-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY94"/>
+  <dimension ref="A1:AY101"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,37 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>105162673</v>
+        <v>105162651</v>
       </c>
       <c r="B2" t="n">
-        <v>89673</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92123</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>658</v>
+        <v>48</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Lappticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Amylocystis lapponica</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Romell) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>598478.0665961816</v>
+        <v>598676</v>
       </c>
       <c r="R2" t="n">
-        <v>7034323.97472812</v>
+        <v>7034543</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -748,19 +743,9 @@
           <t>2022-09-21</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2022-09-21</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -791,53 +776,48 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>105162661</v>
+        <v>119278212</v>
       </c>
       <c r="B3" t="n">
-        <v>77258</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92123</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6446</v>
+        <v>48</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Lappticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Amylocystis lapponica</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Romell) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Norrtannflo värdetrakt, Ång</t>
+          <t>Storstenbäcken, Storstenbäcken, Ång</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>598565.4211947749</v>
+        <v>598364</v>
       </c>
       <c r="R3" t="n">
-        <v>7034299.334760798</v>
+        <v>7034253</v>
       </c>
       <c r="S3" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -861,22 +841,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2022-09-21</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-08-22</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2022-09-21</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-08-22</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -891,53 +861,44 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Jennifer C. Johansson</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Amanda Tas, Erland Lindblad, Steve Daurer</t>
-        </is>
-      </c>
-      <c r="AY3" t="inlineStr">
-        <is>
-          <t>Naturvärdesinventering Y-län</t>
-        </is>
-      </c>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>105162683</v>
+        <v>105162682</v>
       </c>
       <c r="B4" t="n">
-        <v>89356</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92637</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5447</v>
+        <v>67</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Sprickporing</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Diplomitoporus crustulinus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Bres.) Domański</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -947,10 +908,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>598433.0955882302</v>
+        <v>598446</v>
       </c>
       <c r="R4" t="n">
-        <v>7034254.481740041</v>
+        <v>7034268</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -980,19 +941,9 @@
           <t>2022-09-21</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2022-09-21</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1023,15 +974,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>105162647</v>
+        <v>105162663</v>
       </c>
       <c r="B5" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79359</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1039,21 +985,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1063,10 +1009,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>598683.6526260088</v>
+        <v>598562</v>
       </c>
       <c r="R5" t="n">
-        <v>7034582.571159452</v>
+        <v>7034288</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1096,19 +1042,9 @@
           <t>2022-09-21</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2022-09-21</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1139,53 +1075,45 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>105162686</v>
+        <v>105162679</v>
       </c>
       <c r="B6" t="n">
-        <v>89392</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83298</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1202</v>
+        <v>492</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Smalskaftslav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Chaenotheca gracilenta</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) J.Mattsson &amp; Middelb.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
-      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Norrtannflo värdetrakt, Ång</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>598403.1512947362</v>
+        <v>598458</v>
       </c>
       <c r="R6" t="n">
-        <v>7034236.084497525</v>
+        <v>7034272</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1215,28 +1143,17 @@
           <t>2022-09-21</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2022-09-21</t>
         </is>
       </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD6" t="b">
         <v>0</v>
       </c>
       <c r="AE6" t="b">
         <v>0</v>
       </c>
-      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1259,15 +1176,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>105162671</v>
+        <v>105162640</v>
       </c>
       <c r="B7" t="n">
-        <v>89673</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92208</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1284,28 +1196,25 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
-      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Norrtannflo värdetrakt, Ång</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>598499.2723717908</v>
+        <v>598585</v>
       </c>
       <c r="R7" t="n">
-        <v>7034320.147422661</v>
+        <v>7034524</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1335,28 +1244,17 @@
           <t>2022-09-21</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2022-09-21</t>
         </is>
       </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD7" t="b">
         <v>0</v>
       </c>
       <c r="AE7" t="b">
         <v>0</v>
       </c>
-      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1379,15 +1277,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>105162645</v>
+        <v>105162641</v>
       </c>
       <c r="B8" t="n">
-        <v>78569</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92208</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1395,21 +1288,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6458</v>
+        <v>658</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1419,10 +1312,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>598689.5544477052</v>
+        <v>598581</v>
       </c>
       <c r="R8" t="n">
-        <v>7034594.850420655</v>
+        <v>7034566</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1452,24 +1345,9 @@
           <t>2022-09-21</t>
         </is>
       </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2022-09-21</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>På gammal björk</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1500,15 +1378,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>105162639</v>
+        <v>105162643</v>
       </c>
       <c r="B9" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92208</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1516,21 +1389,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>658</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1540,10 +1413,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>598528.0628724884</v>
+        <v>598652</v>
       </c>
       <c r="R9" t="n">
-        <v>7034390.48544223</v>
+        <v>7034649</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1573,19 +1446,9 @@
           <t>2022-09-21</t>
         </is>
       </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2022-09-21</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1616,15 +1479,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>105162665</v>
+        <v>105162649</v>
       </c>
       <c r="B10" t="n">
-        <v>89673</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92208</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1641,12 +1499,12 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1656,10 +1514,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>598543.4428883595</v>
+        <v>598675</v>
       </c>
       <c r="R10" t="n">
-        <v>7034299.105161912</v>
+        <v>7034572</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1689,19 +1547,9 @@
           <t>2022-09-21</t>
         </is>
       </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>2022-09-21</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1732,37 +1580,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>105162650</v>
+        <v>105162654</v>
       </c>
       <c r="B11" t="n">
-        <v>89356</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92208</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>5447</v>
+        <v>658</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1772,10 +1615,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>598682.9852116577</v>
+        <v>598669</v>
       </c>
       <c r="R11" t="n">
-        <v>7034560.596583562</v>
+        <v>7034538</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>
@@ -1805,19 +1648,9 @@
           <t>2022-09-21</t>
         </is>
       </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>2022-09-21</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1848,15 +1681,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>105162669</v>
+        <v>105162658</v>
       </c>
       <c r="B12" t="n">
-        <v>89673</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92208</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1873,12 +1701,12 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1888,10 +1716,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>598523.0711306507</v>
+        <v>598587</v>
       </c>
       <c r="R12" t="n">
-        <v>7034319.536693058</v>
+        <v>7034305</v>
       </c>
       <c r="S12" t="n">
         <v>25</v>
@@ -1921,19 +1749,9 @@
           <t>2022-09-21</t>
         </is>
       </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA12" t="inlineStr">
         <is>
           <t>2022-09-21</t>
-        </is>
-      </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1964,37 +1782,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>105162679</v>
+        <v>105162660</v>
       </c>
       <c r="B13" t="n">
-        <v>73685</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92208</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>492</v>
+        <v>658</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Smalskaftslav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Chaenotheca gracilenta</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) J.Mattsson &amp; Middelb.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -2004,10 +1817,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>598457.6880172207</v>
+        <v>598569</v>
       </c>
       <c r="R13" t="n">
-        <v>7034271.818162072</v>
+        <v>7034299</v>
       </c>
       <c r="S13" t="n">
         <v>25</v>
@@ -2037,19 +1850,9 @@
           <t>2022-09-21</t>
         </is>
       </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA13" t="inlineStr">
         <is>
           <t>2022-09-21</t>
-        </is>
-      </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2080,37 +1883,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>105162682</v>
+        <v>105162664</v>
       </c>
       <c r="B14" t="n">
-        <v>90079</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92208</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>67</v>
+        <v>658</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Sprickporing</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Diplomitoporus crustulinus</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Bres.) Domański</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2120,10 +1918,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>598445.6953263544</v>
+        <v>598553</v>
       </c>
       <c r="R14" t="n">
-        <v>7034267.864130918</v>
+        <v>7034289</v>
       </c>
       <c r="S14" t="n">
         <v>25</v>
@@ -2153,19 +1951,9 @@
           <t>2022-09-21</t>
         </is>
       </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA14" t="inlineStr">
         <is>
           <t>2022-09-21</t>
-        </is>
-      </c>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2196,15 +1984,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>105162688</v>
+        <v>105162665</v>
       </c>
       <c r="B15" t="n">
-        <v>89392</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92208</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2212,21 +1995,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2236,10 +2019,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>598351.3317420568</v>
+        <v>598543</v>
       </c>
       <c r="R15" t="n">
-        <v>7034228.664516605</v>
+        <v>7034299</v>
       </c>
       <c r="S15" t="n">
         <v>25</v>
@@ -2269,19 +2052,9 @@
           <t>2022-09-21</t>
         </is>
       </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA15" t="inlineStr">
         <is>
           <t>2022-09-21</t>
-        </is>
-      </c>
-      <c r="AB15" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2312,15 +2085,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>105162675</v>
+        <v>105162668</v>
       </c>
       <c r="B16" t="n">
-        <v>89673</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92208</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2337,12 +2105,12 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2352,10 +2120,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>598468.1429486654</v>
+        <v>598525</v>
       </c>
       <c r="R16" t="n">
-        <v>7034311.122934629</v>
+        <v>7034303</v>
       </c>
       <c r="S16" t="n">
         <v>25</v>
@@ -2385,19 +2153,9 @@
           <t>2022-09-21</t>
         </is>
       </c>
-      <c r="Z16" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA16" t="inlineStr">
         <is>
           <t>2022-09-21</t>
-        </is>
-      </c>
-      <c r="AB16" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2428,15 +2186,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>105162680</v>
+        <v>105162669</v>
       </c>
       <c r="B17" t="n">
-        <v>89392</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92208</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2444,21 +2197,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2468,10 +2221,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>598456.570873862</v>
+        <v>598523</v>
       </c>
       <c r="R17" t="n">
-        <v>7034278.953019046</v>
+        <v>7034320</v>
       </c>
       <c r="S17" t="n">
         <v>25</v>
@@ -2501,19 +2254,9 @@
           <t>2022-09-21</t>
         </is>
       </c>
-      <c r="Z17" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA17" t="inlineStr">
         <is>
           <t>2022-09-21</t>
-        </is>
-      </c>
-      <c r="AB17" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2544,15 +2287,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>105162654</v>
+        <v>105162671</v>
       </c>
       <c r="B18" t="n">
-        <v>89673</v>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92208</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2569,25 +2307,28 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr"/>
+      <c r="K18" t="inlineStr"/>
+      <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
           <t>Norrtannflo värdetrakt, Ång</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>598669.3193513204</v>
+        <v>598499</v>
       </c>
       <c r="R18" t="n">
-        <v>7034538.220534868</v>
+        <v>7034320</v>
       </c>
       <c r="S18" t="n">
         <v>25</v>
@@ -2617,27 +2358,18 @@
           <t>2022-09-21</t>
         </is>
       </c>
-      <c r="Z18" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA18" t="inlineStr">
         <is>
           <t>2022-09-21</t>
         </is>
       </c>
-      <c r="AB18" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD18" t="b">
         <v>0</v>
       </c>
       <c r="AE18" t="b">
         <v>0</v>
       </c>
+      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
@@ -2660,15 +2392,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>105162642</v>
+        <v>105162673</v>
       </c>
       <c r="B19" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92208</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2676,21 +2403,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>658</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2700,10 +2427,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>598633.0503648665</v>
+        <v>598478</v>
       </c>
       <c r="R19" t="n">
-        <v>7034623.124408778</v>
+        <v>7034324</v>
       </c>
       <c r="S19" t="n">
         <v>25</v>
@@ -2733,19 +2460,9 @@
           <t>2022-09-21</t>
         </is>
       </c>
-      <c r="Z19" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA19" t="inlineStr">
         <is>
           <t>2022-09-21</t>
-        </is>
-      </c>
-      <c r="AB19" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2776,15 +2493,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>105162640</v>
+        <v>105162675</v>
       </c>
       <c r="B20" t="n">
-        <v>89673</v>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92208</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2801,12 +2513,12 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2816,10 +2528,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>598584.5023683378</v>
+        <v>598468</v>
       </c>
       <c r="R20" t="n">
-        <v>7034524.402009442</v>
+        <v>7034311</v>
       </c>
       <c r="S20" t="n">
         <v>25</v>
@@ -2849,19 +2561,9 @@
           <t>2022-09-21</t>
         </is>
       </c>
-      <c r="Z20" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA20" t="inlineStr">
         <is>
           <t>2022-09-21</t>
-        </is>
-      </c>
-      <c r="AB20" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2892,15 +2594,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>105162689</v>
+        <v>119277952</v>
       </c>
       <c r="B21" t="n">
-        <v>89392</v>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92208</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2908,37 +2605,37 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Norrtannflo värdetrakt, Ång</t>
+          <t>Storstenbäcken, Storstenbäcken, Ång</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>598339.3800891516</v>
+        <v>598330</v>
       </c>
       <c r="R21" t="n">
-        <v>7034223.367857412</v>
+        <v>7034204</v>
       </c>
       <c r="S21" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2962,22 +2659,12 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2022-09-21</t>
-        </is>
-      </c>
-      <c r="Z21" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-08-22</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2022-09-21</t>
-        </is>
-      </c>
-      <c r="AB21" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-08-22</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2992,69 +2679,60 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Jennifer C. Johansson</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Amanda Tas, Erland Lindblad, Steve Daurer</t>
-        </is>
-      </c>
-      <c r="AY21" t="inlineStr">
-        <is>
-          <t>Naturvärdesinventering Y-län</t>
-        </is>
-      </c>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>105162687</v>
+        <v>119278034</v>
       </c>
       <c r="B22" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92208</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>220787</v>
+        <v>658</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Norrtannflo värdetrakt, Ång</t>
+          <t>Storstenbäcken, Storstenbäcken, Ång</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>598365.3657141868</v>
+        <v>598358</v>
       </c>
       <c r="R22" t="n">
-        <v>7034224.615513701</v>
+        <v>7034250</v>
       </c>
       <c r="S22" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -3078,27 +2756,12 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2022-09-21</t>
-        </is>
-      </c>
-      <c r="Z22" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-08-22</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2022-09-21</t>
-        </is>
-      </c>
-      <c r="AB22" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>Ett femtiotal</t>
+          <t>2024-08-22</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3113,31 +2776,22 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Jennifer C. Johansson</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Amanda Tas, Erland Lindblad, Steve Daurer</t>
-        </is>
-      </c>
-      <c r="AY22" t="inlineStr">
-        <is>
-          <t>Naturvärdesinventering Y-län</t>
-        </is>
-      </c>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>105162681</v>
+        <v>119278406</v>
       </c>
       <c r="B23" t="n">
-        <v>81236</v>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92208</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3145,37 +2799,37 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1312</v>
+        <v>658</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Norrtannflo värdetrakt, Ång</t>
+          <t>Storstenbäcken, Storstenbäcken, Ång</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>598456.543295697</v>
+        <v>598520</v>
       </c>
       <c r="R23" t="n">
-        <v>7034279.848326988</v>
+        <v>7034228</v>
       </c>
       <c r="S23" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3199,22 +2853,22 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2022-09-21</t>
+          <t>2024-08-22</t>
         </is>
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>15:04</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2022-09-21</t>
+          <t>2024-08-22</t>
         </is>
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>15:04</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3229,31 +2883,22 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Jennifer C. Johansson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Amanda Tas, Erland Lindblad, Steve Daurer</t>
-        </is>
-      </c>
-      <c r="AY23" t="inlineStr">
-        <is>
-          <t>Naturvärdesinventering Y-län</t>
-        </is>
-      </c>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>105162653</v>
+        <v>119278413</v>
       </c>
       <c r="B24" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92208</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3261,37 +2906,37 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6425</v>
+        <v>658</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Norrtannflo värdetrakt, Ång</t>
+          <t>Storstenbäcken, Storstenbäcken, Ång</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>598665.1471693155</v>
+        <v>598404</v>
       </c>
       <c r="R24" t="n">
-        <v>7034542.572174607</v>
+        <v>7034323</v>
       </c>
       <c r="S24" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3315,22 +2960,12 @@
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>2022-09-21</t>
-        </is>
-      </c>
-      <c r="Z24" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-08-22</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>2022-09-21</t>
-        </is>
-      </c>
-      <c r="AB24" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-08-22</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3345,31 +2980,22 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Jennifer C. Johansson</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Amanda Tas, Erland Lindblad, Steve Daurer</t>
-        </is>
-      </c>
-      <c r="AY24" t="inlineStr">
-        <is>
-          <t>Naturvärdesinventering Y-län</t>
-        </is>
-      </c>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>105162670</v>
+        <v>119278420</v>
       </c>
       <c r="B25" t="n">
-        <v>89412</v>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92208</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3377,37 +3003,37 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>5442</v>
+        <v>658</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Norrtannflo värdetrakt, Ång</t>
+          <t>Storstenbäcken, Storstenbäcken, Ång</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>598518.8847205178</v>
+        <v>598415</v>
       </c>
       <c r="R25" t="n">
-        <v>7034353.46107634</v>
+        <v>7034330</v>
       </c>
       <c r="S25" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3431,22 +3057,12 @@
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>2022-09-21</t>
-        </is>
-      </c>
-      <c r="Z25" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-08-22</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>2022-09-21</t>
-        </is>
-      </c>
-      <c r="AB25" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-08-22</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3461,31 +3077,22 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Jennifer C. Johansson</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Amanda Tas, Erland Lindblad, Steve Daurer</t>
-        </is>
-      </c>
-      <c r="AY25" t="inlineStr">
-        <is>
-          <t>Naturvärdesinventering Y-län</t>
-        </is>
-      </c>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>105162644</v>
+        <v>119278432</v>
       </c>
       <c r="B26" t="n">
-        <v>55608</v>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92208</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3493,37 +3100,37 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>102612</v>
+        <v>658</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Norrtannflo värdetrakt, Ång</t>
+          <t>Storstenbäcken, Storstenbäcken, Ång</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>598679.6661011097</v>
+        <v>598410</v>
       </c>
       <c r="R26" t="n">
-        <v>7034595.441160627</v>
+        <v>7034317</v>
       </c>
       <c r="S26" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3547,22 +3154,12 @@
       </c>
       <c r="Y26" t="inlineStr">
         <is>
-          <t>2022-09-21</t>
-        </is>
-      </c>
-      <c r="Z26" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-08-22</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>2022-09-21</t>
-        </is>
-      </c>
-      <c r="AB26" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-08-22</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3577,31 +3174,22 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Jennifer C. Johansson</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Amanda Tas, Erland Lindblad, Steve Daurer</t>
-        </is>
-      </c>
-      <c r="AY26" t="inlineStr">
-        <is>
-          <t>Naturvärdesinventering Y-län</t>
-        </is>
-      </c>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>105162638</v>
+        <v>119278466</v>
       </c>
       <c r="B27" t="n">
-        <v>56395</v>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92208</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3609,41 +3197,37 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>100109</v>
+        <v>658</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
-      <c r="K27" t="inlineStr"/>
-      <c r="L27" t="inlineStr"/>
-      <c r="M27" t="inlineStr"/>
-      <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Norrtannflo värdetrakt, Ång</t>
+          <t>Storstenbäcken, Storstenbäcken, Ång</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>598399.3875275487</v>
+        <v>598446</v>
       </c>
       <c r="R27" t="n">
-        <v>7034300.044033484</v>
+        <v>7034308</v>
       </c>
       <c r="S27" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3667,22 +3251,12 @@
       </c>
       <c r="Y27" t="inlineStr">
         <is>
-          <t>2022-09-21</t>
-        </is>
-      </c>
-      <c r="Z27" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-08-22</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>2022-09-21</t>
-        </is>
-      </c>
-      <c r="AB27" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-08-22</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3697,31 +3271,22 @@
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Jennifer C. Johansson</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Amanda Tas, Erland Lindblad, Steve Daurer</t>
-        </is>
-      </c>
-      <c r="AY27" t="inlineStr">
-        <is>
-          <t>Naturvärdesinventering Y-län</t>
-        </is>
-      </c>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>105162663</v>
+        <v>119278487</v>
       </c>
       <c r="B28" t="n">
-        <v>77541</v>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92208</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3729,37 +3294,37 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>185</v>
+        <v>658</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Norrtannflo värdetrakt, Ång</t>
+          <t>Storstenbäcken, Storstenbäcken, Ång</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>598562.6285068047</v>
+        <v>598580</v>
       </c>
       <c r="R28" t="n">
-        <v>7034288.046699189</v>
+        <v>7034264</v>
       </c>
       <c r="S28" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3783,22 +3348,22 @@
       </c>
       <c r="Y28" t="inlineStr">
         <is>
-          <t>2022-09-21</t>
+          <t>2024-08-22</t>
         </is>
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>15:16</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>2022-09-21</t>
+          <t>2024-08-22</t>
         </is>
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>15:16</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3813,31 +3378,22 @@
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Jennifer C. Johansson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Amanda Tas, Erland Lindblad, Steve Daurer</t>
-        </is>
-      </c>
-      <c r="AY28" t="inlineStr">
-        <is>
-          <t>Naturvärdesinventering Y-län</t>
-        </is>
-      </c>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>105162652</v>
+        <v>119278518</v>
       </c>
       <c r="B29" t="n">
-        <v>81236</v>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92208</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3845,37 +3401,37 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>1312</v>
+        <v>658</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Norrtannflo värdetrakt, Ång</t>
+          <t>Storstenbäcken, Storstenbäcken, Ång</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>598664.1263608974</v>
+        <v>598471</v>
       </c>
       <c r="R29" t="n">
-        <v>7034546.573054653</v>
+        <v>7034306</v>
       </c>
       <c r="S29" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3899,22 +3455,12 @@
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>2022-09-21</t>
-        </is>
-      </c>
-      <c r="Z29" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-08-22</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>2022-09-21</t>
-        </is>
-      </c>
-      <c r="AB29" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-08-22</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3929,31 +3475,22 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Jennifer C. Johansson</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Amanda Tas, Erland Lindblad, Steve Daurer</t>
-        </is>
-      </c>
-      <c r="AY29" t="inlineStr">
-        <is>
-          <t>Naturvärdesinventering Y-län</t>
-        </is>
-      </c>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>105162646</v>
+        <v>119278576</v>
       </c>
       <c r="B30" t="n">
-        <v>89392</v>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92208</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3961,37 +3498,37 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Norrtannflo värdetrakt, Ång</t>
+          <t>Storstenbäcken, Storstenbäcken, Ång</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>598684.8728800912</v>
+        <v>598475</v>
       </c>
       <c r="R30" t="n">
-        <v>7034586.641183519</v>
+        <v>7034340</v>
       </c>
       <c r="S30" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -4015,22 +3552,12 @@
       </c>
       <c r="Y30" t="inlineStr">
         <is>
-          <t>2022-09-21</t>
-        </is>
-      </c>
-      <c r="Z30" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-08-22</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>2022-09-21</t>
-        </is>
-      </c>
-      <c r="AB30" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-08-22</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4045,31 +3572,22 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Jennifer C. Johansson</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Amanda Tas, Erland Lindblad, Steve Daurer</t>
-        </is>
-      </c>
-      <c r="AY30" t="inlineStr">
-        <is>
-          <t>Naturvärdesinventering Y-län</t>
-        </is>
-      </c>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>105162643</v>
+        <v>119278599</v>
       </c>
       <c r="B31" t="n">
-        <v>89673</v>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92208</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4086,28 +3604,28 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Norrtannflo värdetrakt, Ång</t>
+          <t>Storstenbäcken, Storstenbäcken, Ång</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>598651.9840327313</v>
+        <v>598483</v>
       </c>
       <c r="R31" t="n">
-        <v>7034649.246558244</v>
+        <v>7034339</v>
       </c>
       <c r="S31" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -4131,22 +3649,12 @@
       </c>
       <c r="Y31" t="inlineStr">
         <is>
-          <t>2022-09-21</t>
-        </is>
-      </c>
-      <c r="Z31" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-08-22</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>2022-09-21</t>
-        </is>
-      </c>
-      <c r="AB31" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-08-22</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4161,31 +3669,22 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Jennifer C. Johansson</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Amanda Tas, Erland Lindblad, Steve Daurer</t>
-        </is>
-      </c>
-      <c r="AY31" t="inlineStr">
-        <is>
-          <t>Naturvärdesinventering Y-län</t>
-        </is>
-      </c>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>105162668</v>
+        <v>119278693</v>
       </c>
       <c r="B32" t="n">
-        <v>89673</v>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92208</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4202,28 +3701,28 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Norrtannflo värdetrakt, Ång</t>
+          <t>Storstenbäcken, Storstenbäcken, Ång</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>598525.3884912109</v>
+        <v>598485</v>
       </c>
       <c r="R32" t="n">
-        <v>7034302.581276352</v>
+        <v>7034362</v>
       </c>
       <c r="S32" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -4247,22 +3746,12 @@
       </c>
       <c r="Y32" t="inlineStr">
         <is>
-          <t>2022-09-21</t>
-        </is>
-      </c>
-      <c r="Z32" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-08-22</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>2022-09-21</t>
-        </is>
-      </c>
-      <c r="AB32" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-08-22</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4277,69 +3766,60 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Jennifer C. Johansson</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Amanda Tas, Erland Lindblad, Steve Daurer</t>
-        </is>
-      </c>
-      <c r="AY32" t="inlineStr">
-        <is>
-          <t>Naturvärdesinventering Y-län</t>
-        </is>
-      </c>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>105162651</v>
+        <v>119278756</v>
       </c>
       <c r="B33" t="n">
-        <v>89577</v>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92208</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>48</v>
+        <v>658</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Lappticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Amylocystis lapponica</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Romell) Singer</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Norrtannflo värdetrakt, Ång</t>
+          <t>Storstenbäcken, Storstenbäcken, Ång</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>598676.3665181248</v>
+        <v>598485</v>
       </c>
       <c r="R33" t="n">
-        <v>7034542.470507436</v>
+        <v>7034367</v>
       </c>
       <c r="S33" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4363,22 +3843,12 @@
       </c>
       <c r="Y33" t="inlineStr">
         <is>
-          <t>2022-09-21</t>
-        </is>
-      </c>
-      <c r="Z33" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-08-22</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
         <is>
-          <t>2022-09-21</t>
-        </is>
-      </c>
-      <c r="AB33" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-08-22</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4393,31 +3863,22 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Jennifer C. Johansson</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Amanda Tas, Erland Lindblad, Steve Daurer</t>
-        </is>
-      </c>
-      <c r="AY33" t="inlineStr">
-        <is>
-          <t>Naturvärdesinventering Y-län</t>
-        </is>
-      </c>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>105162658</v>
+        <v>119279131</v>
       </c>
       <c r="B34" t="n">
-        <v>89673</v>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92208</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4434,28 +3895,28 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Norrtannflo värdetrakt, Ång</t>
+          <t>Storstenbäcken, Storstenbäcken, Ång</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>598587.2476222051</v>
+        <v>598616</v>
       </c>
       <c r="R34" t="n">
-        <v>7034304.488671181</v>
+        <v>7034552</v>
       </c>
       <c r="S34" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4479,22 +3940,12 @@
       </c>
       <c r="Y34" t="inlineStr">
         <is>
-          <t>2022-09-21</t>
-        </is>
-      </c>
-      <c r="Z34" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-08-22</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
         <is>
-          <t>2022-09-21</t>
-        </is>
-      </c>
-      <c r="AB34" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-08-22</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4509,31 +3960,22 @@
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Jennifer C. Johansson</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Amanda Tas, Erland Lindblad, Steve Daurer</t>
-        </is>
-      </c>
-      <c r="AY34" t="inlineStr">
-        <is>
-          <t>Naturvärdesinventering Y-län</t>
-        </is>
-      </c>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>105162641</v>
+        <v>119280133</v>
       </c>
       <c r="B35" t="n">
-        <v>89673</v>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92208</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4550,28 +3992,28 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Norrtannflo värdetrakt, Ång</t>
+          <t>Storstenbäcken, Storstenbäcken, Ång</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>598580.9634026452</v>
+        <v>598369</v>
       </c>
       <c r="R35" t="n">
-        <v>7034566.408874094</v>
+        <v>7034251</v>
       </c>
       <c r="S35" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4595,22 +4037,12 @@
       </c>
       <c r="Y35" t="inlineStr">
         <is>
-          <t>2022-09-21</t>
-        </is>
-      </c>
-      <c r="Z35" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-08-22</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
         <is>
-          <t>2022-09-21</t>
-        </is>
-      </c>
-      <c r="AB35" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-08-22</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4625,31 +4057,22 @@
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Jennifer C. Johansson</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Amanda Tas, Erland Lindblad, Steve Daurer</t>
-        </is>
-      </c>
-      <c r="AY35" t="inlineStr">
-        <is>
-          <t>Naturvärdesinventering Y-län</t>
-        </is>
-      </c>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>105162637</v>
+        <v>105162646</v>
       </c>
       <c r="B36" t="n">
-        <v>56540</v>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4657,21 +4080,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>103021</v>
+        <v>1202</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4681,10 +4104,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>598554.5011970901</v>
+        <v>598685</v>
       </c>
       <c r="R36" t="n">
-        <v>7034435.210535397</v>
+        <v>7034587</v>
       </c>
       <c r="S36" t="n">
         <v>25</v>
@@ -4714,19 +4137,9 @@
           <t>2022-09-21</t>
         </is>
       </c>
-      <c r="Z36" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA36" t="inlineStr">
         <is>
           <t>2022-09-21</t>
-        </is>
-      </c>
-      <c r="AB36" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4757,15 +4170,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>105162664</v>
+        <v>105162648</v>
       </c>
       <c r="B37" t="n">
-        <v>89673</v>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4773,21 +4181,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4797,10 +4205,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>598553.6219634123</v>
+        <v>598676</v>
       </c>
       <c r="R37" t="n">
-        <v>7034289.113218799</v>
+        <v>7034577</v>
       </c>
       <c r="S37" t="n">
         <v>25</v>
@@ -4830,19 +4238,9 @@
           <t>2022-09-21</t>
         </is>
       </c>
-      <c r="Z37" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA37" t="inlineStr">
         <is>
           <t>2022-09-21</t>
-        </is>
-      </c>
-      <c r="AB37" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4873,15 +4271,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>105162666</v>
+        <v>105162656</v>
       </c>
       <c r="B38" t="n">
-        <v>89406</v>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4889,21 +4282,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>1204</v>
+        <v>1202</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4913,10 +4306,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>598540.3741062534</v>
+        <v>598644</v>
       </c>
       <c r="R38" t="n">
-        <v>7034296.770166832</v>
+        <v>7034327</v>
       </c>
       <c r="S38" t="n">
         <v>25</v>
@@ -4946,19 +4339,9 @@
           <t>2022-09-21</t>
         </is>
       </c>
-      <c r="Z38" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA38" t="inlineStr">
         <is>
           <t>2022-09-21</t>
-        </is>
-      </c>
-      <c r="AB38" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4989,37 +4372,32 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>105162659</v>
+        <v>105162680</v>
       </c>
       <c r="B39" t="n">
-        <v>89832</v>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>1209</v>
+        <v>1202</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -5029,10 +4407,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>598584.0131920731</v>
+        <v>598457</v>
       </c>
       <c r="R39" t="n">
-        <v>7034307.52544321</v>
+        <v>7034279</v>
       </c>
       <c r="S39" t="n">
         <v>25</v>
@@ -5062,19 +4440,9 @@
           <t>2022-09-21</t>
         </is>
       </c>
-      <c r="Z39" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA39" t="inlineStr">
         <is>
           <t>2022-09-21</t>
-        </is>
-      </c>
-      <c r="AB39" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5105,50 +4473,48 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>105162678</v>
+        <v>105162686</v>
       </c>
       <c r="B40" t="n">
-        <v>89832</v>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>1209</v>
+        <v>1202</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
+      <c r="J40" t="inlineStr"/>
+      <c r="K40" t="inlineStr"/>
+      <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
           <t>Norrtannflo värdetrakt, Ång</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>598462.4603660881</v>
+        <v>598403</v>
       </c>
       <c r="R40" t="n">
-        <v>7034291.680620615</v>
+        <v>7034236</v>
       </c>
       <c r="S40" t="n">
         <v>25</v>
@@ -5178,27 +4544,18 @@
           <t>2022-09-21</t>
         </is>
       </c>
-      <c r="Z40" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA40" t="inlineStr">
         <is>
           <t>2022-09-21</t>
         </is>
       </c>
-      <c r="AB40" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD40" t="b">
         <v>0</v>
       </c>
       <c r="AE40" t="b">
         <v>0</v>
       </c>
+      <c r="AF40" t="inlineStr"/>
       <c r="AG40" t="b">
         <v>0</v>
       </c>
@@ -5221,15 +4578,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>105162649</v>
+        <v>105162688</v>
       </c>
       <c r="B41" t="n">
-        <v>89673</v>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5237,21 +4589,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -5261,10 +4613,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>598674.9923538342</v>
+        <v>598351</v>
       </c>
       <c r="R41" t="n">
-        <v>7034572.446898004</v>
+        <v>7034228</v>
       </c>
       <c r="S41" t="n">
         <v>25</v>
@@ -5294,19 +4646,9 @@
           <t>2022-09-21</t>
         </is>
       </c>
-      <c r="Z41" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA41" t="inlineStr">
         <is>
           <t>2022-09-21</t>
-        </is>
-      </c>
-      <c r="AB41" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5337,15 +4679,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>105162648</v>
+        <v>105162689</v>
       </c>
       <c r="B42" t="n">
-        <v>89392</v>
-      </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5377,10 +4714,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>598675.764406749</v>
+        <v>598340</v>
       </c>
       <c r="R42" t="n">
-        <v>7034576.503092259</v>
+        <v>7034224</v>
       </c>
       <c r="S42" t="n">
         <v>25</v>
@@ -5410,19 +4747,9 @@
           <t>2022-09-21</t>
         </is>
       </c>
-      <c r="Z42" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA42" t="inlineStr">
         <is>
           <t>2022-09-21</t>
-        </is>
-      </c>
-      <c r="AB42" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5453,15 +4780,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>105162662</v>
+        <v>105162690</v>
       </c>
       <c r="B43" t="n">
-        <v>78098</v>
-      </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5469,21 +4791,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6453</v>
+        <v>1202</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5493,10 +4815,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>598565.4211947749</v>
+        <v>598324</v>
       </c>
       <c r="R43" t="n">
-        <v>7034299.334760798</v>
+        <v>7034215</v>
       </c>
       <c r="S43" t="n">
         <v>25</v>
@@ -5526,19 +4848,9 @@
           <t>2022-09-21</t>
         </is>
       </c>
-      <c r="Z43" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA43" t="inlineStr">
         <is>
           <t>2022-09-21</t>
-        </is>
-      </c>
-      <c r="AB43" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5569,53 +4881,48 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>105162685</v>
+        <v>119277958</v>
       </c>
       <c r="B44" t="n">
-        <v>89356</v>
-      </c>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>5447</v>
+        <v>1202</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Norrtannflo värdetrakt, Ång</t>
+          <t>Storstenbäcken, Storstenbäcken, Ång</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>598424.7374071567</v>
+        <v>598330</v>
       </c>
       <c r="R44" t="n">
-        <v>7034263.634064318</v>
+        <v>7034182</v>
       </c>
       <c r="S44" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -5639,22 +4946,12 @@
       </c>
       <c r="Y44" t="inlineStr">
         <is>
-          <t>2022-09-21</t>
-        </is>
-      </c>
-      <c r="Z44" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-08-22</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
         <is>
-          <t>2022-09-21</t>
-        </is>
-      </c>
-      <c r="AB44" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-08-22</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5669,31 +4966,22 @@
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Jennifer C. Johansson</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Amanda Tas, Erland Lindblad, Steve Daurer</t>
-        </is>
-      </c>
-      <c r="AY44" t="inlineStr">
-        <is>
-          <t>Naturvärdesinventering Y-län</t>
-        </is>
-      </c>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>105162672</v>
+        <v>119278019</v>
       </c>
       <c r="B45" t="n">
-        <v>81236</v>
-      </c>
-      <c r="C45" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5701,37 +4989,37 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>1312</v>
+        <v>1202</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Norrtannflo värdetrakt, Ång</t>
+          <t>Storstenbäcken, Storstenbäcken, Ång</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>598485.9627380462</v>
+        <v>598348</v>
       </c>
       <c r="R45" t="n">
-        <v>7034315.256552599</v>
+        <v>7034205</v>
       </c>
       <c r="S45" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -5755,22 +5043,12 @@
       </c>
       <c r="Y45" t="inlineStr">
         <is>
-          <t>2022-09-21</t>
-        </is>
-      </c>
-      <c r="Z45" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-08-22</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
         <is>
-          <t>2022-09-21</t>
-        </is>
-      </c>
-      <c r="AB45" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-08-22</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5785,69 +5063,60 @@
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Jennifer C. Johansson</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Amanda Tas, Erland Lindblad, Steve Daurer</t>
-        </is>
-      </c>
-      <c r="AY45" t="inlineStr">
-        <is>
-          <t>Naturvärdesinventering Y-län</t>
-        </is>
-      </c>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>105162667</v>
+        <v>119278582</v>
       </c>
       <c r="B46" t="n">
-        <v>78503</v>
-      </c>
-      <c r="C46" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6456</v>
+        <v>1202</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Norrtannflo värdetrakt, Ång</t>
+          <t>Storstenbäcken, Storstenbäcken, Ång</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>598537.3671629052</v>
+        <v>598478</v>
       </c>
       <c r="R46" t="n">
-        <v>7034306.983222424</v>
+        <v>7034333</v>
       </c>
       <c r="S46" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -5871,22 +5140,12 @@
       </c>
       <c r="Y46" t="inlineStr">
         <is>
-          <t>2022-09-21</t>
-        </is>
-      </c>
-      <c r="Z46" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-08-22</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
         <is>
-          <t>2022-09-21</t>
-        </is>
-      </c>
-      <c r="AB46" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-08-22</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5901,31 +5160,22 @@
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Jennifer C. Johansson</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Amanda Tas, Erland Lindblad, Steve Daurer</t>
-        </is>
-      </c>
-      <c r="AY46" t="inlineStr">
-        <is>
-          <t>Naturvärdesinventering Y-län</t>
-        </is>
-      </c>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>105162677</v>
+        <v>119279160</v>
       </c>
       <c r="B47" t="n">
-        <v>81236</v>
-      </c>
-      <c r="C47" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5933,37 +5183,37 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>1312</v>
+        <v>1202</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Norrtannflo värdetrakt, Ång</t>
+          <t>Storstenbäcken, Storstenbäcken, Ång</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>598451.3575085286</v>
+        <v>598621</v>
       </c>
       <c r="R47" t="n">
-        <v>7034302.540521959</v>
+        <v>7034555</v>
       </c>
       <c r="S47" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -5987,22 +5237,12 @@
       </c>
       <c r="Y47" t="inlineStr">
         <is>
-          <t>2022-09-21</t>
-        </is>
-      </c>
-      <c r="Z47" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-08-22</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
         <is>
-          <t>2022-09-21</t>
-        </is>
-      </c>
-      <c r="AB47" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-08-22</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -6017,31 +5257,22 @@
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Jennifer C. Johansson</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Amanda Tas, Erland Lindblad, Steve Daurer</t>
-        </is>
-      </c>
-      <c r="AY47" t="inlineStr">
-        <is>
-          <t>Naturvärdesinventering Y-län</t>
-        </is>
-      </c>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>105162656</v>
+        <v>119279180</v>
       </c>
       <c r="B48" t="n">
-        <v>89392</v>
-      </c>
-      <c r="C48" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -6069,17 +5300,17 @@
       <c r="I48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Norrtannflo värdetrakt, Ång</t>
+          <t>Storstenbäcken, Storstenbäcken, Ång</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>598643.974858024</v>
+        <v>598834</v>
       </c>
       <c r="R48" t="n">
-        <v>7034327.298420135</v>
+        <v>7034566</v>
       </c>
       <c r="S48" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -6103,22 +5334,22 @@
       </c>
       <c r="Y48" t="inlineStr">
         <is>
-          <t>2022-09-21</t>
+          <t>2024-08-22</t>
         </is>
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>16:01</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
         <is>
-          <t>2022-09-21</t>
+          <t>2024-08-22</t>
         </is>
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>16:01</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -6133,69 +5364,60 @@
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Jennifer C. Johansson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Amanda Tas, Erland Lindblad, Steve Daurer</t>
-        </is>
-      </c>
-      <c r="AY48" t="inlineStr">
-        <is>
-          <t>Naturvärdesinventering Y-län</t>
-        </is>
-      </c>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AY48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>105162674</v>
+        <v>119280135</v>
       </c>
       <c r="B49" t="n">
-        <v>89832</v>
-      </c>
-      <c r="C49" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>1209</v>
+        <v>1202</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Norrtannflo värdetrakt, Ång</t>
+          <t>Storstenbäcken, Storstenbäcken, Ång</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>598473.9909568042</v>
+        <v>598365</v>
       </c>
       <c r="R49" t="n">
-        <v>7034325.193376983</v>
+        <v>7034248</v>
       </c>
       <c r="S49" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -6219,22 +5441,12 @@
       </c>
       <c r="Y49" t="inlineStr">
         <is>
-          <t>2022-09-21</t>
-        </is>
-      </c>
-      <c r="Z49" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-08-22</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
         <is>
-          <t>2022-09-21</t>
-        </is>
-      </c>
-      <c r="AB49" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-08-22</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6249,53 +5461,44 @@
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Jennifer C. Johansson</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Amanda Tas, Erland Lindblad, Steve Daurer</t>
-        </is>
-      </c>
-      <c r="AY49" t="inlineStr">
-        <is>
-          <t>Naturvärdesinventering Y-län</t>
-        </is>
-      </c>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>105162684</v>
+        <v>105162666</v>
       </c>
       <c r="B50" t="n">
-        <v>89997</v>
-      </c>
-      <c r="C50" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91923</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>5454</v>
+        <v>1204</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Hornvaxskinn</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Crustoderma corneum</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Bourdot &amp; Galzin) Nakasone</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -6305,10 +5508,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>598427.8200871241</v>
+        <v>598540</v>
       </c>
       <c r="R50" t="n">
-        <v>7034265.521312298</v>
+        <v>7034297</v>
       </c>
       <c r="S50" t="n">
         <v>25</v>
@@ -6338,19 +5541,9 @@
           <t>2022-09-21</t>
         </is>
       </c>
-      <c r="Z50" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA50" t="inlineStr">
         <is>
           <t>2022-09-21</t>
-        </is>
-      </c>
-      <c r="AB50" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6381,15 +5574,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>105162660</v>
+        <v>105162659</v>
       </c>
       <c r="B51" t="n">
-        <v>89673</v>
-      </c>
-      <c r="C51" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92369</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6397,21 +5585,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>658</v>
+        <v>1209</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -6421,10 +5609,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>598569.4554912579</v>
+        <v>598584</v>
       </c>
       <c r="R51" t="n">
-        <v>7034299.459170109</v>
+        <v>7034307</v>
       </c>
       <c r="S51" t="n">
         <v>25</v>
@@ -6454,19 +5642,9 @@
           <t>2022-09-21</t>
         </is>
       </c>
-      <c r="Z51" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA51" t="inlineStr">
         <is>
           <t>2022-09-21</t>
-        </is>
-      </c>
-      <c r="AB51" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6497,15 +5675,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>106564418</v>
+        <v>105162674</v>
       </c>
       <c r="B52" t="n">
-        <v>78569</v>
-      </c>
-      <c r="C52" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92369</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6513,40 +5686,37 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6458</v>
+        <v>1209</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
-      <c r="J52" t="inlineStr"/>
-      <c r="K52" t="inlineStr"/>
-      <c r="N52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Blåbärshällarna, Ång</t>
+          <t>Norrtannflo värdetrakt, Ång</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>598668.0119067493</v>
+        <v>598474</v>
       </c>
       <c r="R52" t="n">
-        <v>7034493.375391286</v>
+        <v>7034325</v>
       </c>
       <c r="S52" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -6570,22 +5740,12 @@
       </c>
       <c r="Y52" t="inlineStr">
         <is>
-          <t>2023-02-09</t>
-        </is>
-      </c>
-      <c r="Z52" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-09-21</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
         <is>
-          <t>2023-02-09</t>
-        </is>
-      </c>
-      <c r="AB52" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-09-21</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6594,49 +5754,32 @@
       <c r="AE52" t="b">
         <v>0</v>
       </c>
-      <c r="AF52" t="inlineStr"/>
       <c r="AG52" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ52" t="inlineStr">
-        <is>
-          <t>asp</t>
-        </is>
-      </c>
-      <c r="AK52" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
-      <c r="AO52" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
       </c>
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Jennifer C. Johansson</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
-        </is>
-      </c>
-      <c r="AY52" t="inlineStr"/>
+          <t>Amanda Tas, Erland Lindblad, Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AY52" t="inlineStr">
+        <is>
+          <t>Naturvärdesinventering Y-län</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>105162657</v>
+        <v>105162678</v>
       </c>
       <c r="B53" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C53" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92369</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6644,21 +5787,21 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6425</v>
+        <v>1209</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -6668,10 +5811,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>598596.3093720882</v>
+        <v>598463</v>
       </c>
       <c r="R53" t="n">
-        <v>7034301.631649011</v>
+        <v>7034292</v>
       </c>
       <c r="S53" t="n">
         <v>25</v>
@@ -6701,19 +5844,9 @@
           <t>2022-09-21</t>
         </is>
       </c>
-      <c r="Z53" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA53" t="inlineStr">
         <is>
           <t>2022-09-21</t>
-        </is>
-      </c>
-      <c r="AB53" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6744,15 +5877,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>105162676</v>
+        <v>105162652</v>
       </c>
       <c r="B54" t="n">
-        <v>81236</v>
-      </c>
-      <c r="C54" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83173</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6784,10 +5912,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>598465.2052018608</v>
+        <v>598664</v>
       </c>
       <c r="R54" t="n">
-        <v>7034319.09776164</v>
+        <v>7034546</v>
       </c>
       <c r="S54" t="n">
         <v>25</v>
@@ -6817,19 +5945,9 @@
           <t>2022-09-21</t>
         </is>
       </c>
-      <c r="Z54" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA54" t="inlineStr">
         <is>
           <t>2022-09-21</t>
-        </is>
-      </c>
-      <c r="AB54" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6860,15 +5978,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>119278582</v>
+        <v>105162672</v>
       </c>
       <c r="B55" t="n">
-        <v>90562</v>
-      </c>
-      <c r="C55" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83173</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6876,37 +5989,37 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>1202</v>
+        <v>1312</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Storstenbäcken, Storstenbäcken, Ång</t>
+          <t>Norrtannflo värdetrakt, Ång</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>598478</v>
+        <v>598486</v>
       </c>
       <c r="R55" t="n">
-        <v>7034333</v>
+        <v>7034315</v>
       </c>
       <c r="S55" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
@@ -6930,12 +6043,12 @@
       </c>
       <c r="Y55" t="inlineStr">
         <is>
-          <t>2024-08-22</t>
+          <t>2022-09-21</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
         <is>
-          <t>2024-08-22</t>
+          <t>2022-09-21</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6950,27 +6063,26 @@
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Jennifer C. Johansson</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
-        </is>
-      </c>
-      <c r="AY55" t="inlineStr"/>
+          <t>Amanda Tas, Erland Lindblad, Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AY55" t="inlineStr">
+        <is>
+          <t>Naturvärdesinventering Y-län</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>119278693</v>
+        <v>105162676</v>
       </c>
       <c r="B56" t="n">
-        <v>90846</v>
-      </c>
-      <c r="C56" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83173</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6978,37 +6090,37 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>658</v>
+        <v>1312</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
-          <t>Storstenbäcken, Storstenbäcken, Ång</t>
+          <t>Norrtannflo värdetrakt, Ång</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>598485</v>
+        <v>598465</v>
       </c>
       <c r="R56" t="n">
-        <v>7034362</v>
+        <v>7034319</v>
       </c>
       <c r="S56" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -7032,12 +6144,12 @@
       </c>
       <c r="Y56" t="inlineStr">
         <is>
-          <t>2024-08-22</t>
+          <t>2022-09-21</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
         <is>
-          <t>2024-08-22</t>
+          <t>2022-09-21</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -7052,65 +6164,64 @@
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Jennifer C. Johansson</t>
         </is>
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
-        </is>
-      </c>
-      <c r="AY56" t="inlineStr"/>
+          <t>Amanda Tas, Erland Lindblad, Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AY56" t="inlineStr">
+        <is>
+          <t>Naturvärdesinventering Y-län</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>119280121</v>
+        <v>105162677</v>
       </c>
       <c r="B57" t="n">
-        <v>58166</v>
-      </c>
-      <c r="C57" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83173</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>208249</v>
+        <v>1312</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Vanlig groda</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Rana temporaria</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
-          <t>Storstenbäcken, Storstenbäcken, Ång</t>
+          <t>Norrtannflo värdetrakt, Ång</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>598391</v>
+        <v>598451</v>
       </c>
       <c r="R57" t="n">
-        <v>7034279</v>
+        <v>7034303</v>
       </c>
       <c r="S57" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T57" t="inlineStr">
         <is>
@@ -7134,22 +6245,12 @@
       </c>
       <c r="Y57" t="inlineStr">
         <is>
-          <t>2024-08-22</t>
-        </is>
-      </c>
-      <c r="Z57" t="inlineStr">
-        <is>
-          <t>16:47</t>
+          <t>2022-09-21</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
         <is>
-          <t>2024-08-22</t>
-        </is>
-      </c>
-      <c r="AB57" t="inlineStr">
-        <is>
-          <t>16:47</t>
+          <t>2022-09-21</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -7164,27 +6265,26 @@
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Jennifer C. Johansson</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
-        </is>
-      </c>
-      <c r="AY57" t="inlineStr"/>
+          <t>Amanda Tas, Erland Lindblad, Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AY57" t="inlineStr">
+        <is>
+          <t>Naturvärdesinventering Y-län</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>119278842</v>
+        <v>105162681</v>
       </c>
       <c r="B58" t="n">
-        <v>78526</v>
-      </c>
-      <c r="C58" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83173</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7192,37 +6292,37 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>6425</v>
+        <v>1312</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
-          <t>Storstenbäcken, Storstenbäcken, Ång</t>
+          <t>Norrtannflo värdetrakt, Ång</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>598487</v>
+        <v>598457</v>
       </c>
       <c r="R58" t="n">
-        <v>7034370</v>
+        <v>7034279</v>
       </c>
       <c r="S58" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>
@@ -7246,12 +6346,12 @@
       </c>
       <c r="Y58" t="inlineStr">
         <is>
-          <t>2024-08-22</t>
+          <t>2022-09-21</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
         <is>
-          <t>2024-08-22</t>
+          <t>2022-09-21</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -7266,49 +6366,48 @@
       <c r="AT58" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Jennifer C. Johansson</t>
         </is>
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
-        </is>
-      </c>
-      <c r="AY58" t="inlineStr"/>
+          <t>Amanda Tas, Erland Lindblad, Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AY58" t="inlineStr">
+        <is>
+          <t>Naturvärdesinventering Y-län</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>119279180</v>
+        <v>119279419</v>
       </c>
       <c r="B59" t="n">
-        <v>90562</v>
-      </c>
-      <c r="C59" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>101299</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>1202</v>
+        <v>1365</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lappranunkel</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Coptidium lapponicum</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Tzvelev</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -7318,10 +6417,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>598834</v>
+        <v>598601</v>
       </c>
       <c r="R59" t="n">
-        <v>7034566</v>
+        <v>7034602</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -7353,7 +6452,7 @@
       </c>
       <c r="Z59" t="inlineStr">
         <is>
-          <t>16:01</t>
+          <t>16:16</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
@@ -7363,7 +6462,7 @@
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>16:01</t>
+          <t>16:16</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -7390,37 +6489,32 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>119280133</v>
+        <v>119279544</v>
       </c>
       <c r="B60" t="n">
-        <v>90846</v>
-      </c>
-      <c r="C60" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>101299</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>658</v>
+        <v>1365</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Lappranunkel</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Coptidium lapponicum</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(L.) Tzvelev</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -7430,13 +6524,13 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>598369</v>
+        <v>598603</v>
       </c>
       <c r="R60" t="n">
-        <v>7034251</v>
+        <v>7034615</v>
       </c>
       <c r="S60" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T60" t="inlineStr">
         <is>
@@ -7492,15 +6586,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>119277952</v>
+        <v>105162670</v>
       </c>
       <c r="B61" t="n">
-        <v>90846</v>
-      </c>
-      <c r="C61" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91930</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7508,37 +6597,37 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>658</v>
+        <v>5442</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
-          <t>Storstenbäcken, Storstenbäcken, Ång</t>
+          <t>Norrtannflo värdetrakt, Ång</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>598330</v>
+        <v>598519</v>
       </c>
       <c r="R61" t="n">
-        <v>7034204</v>
+        <v>7034354</v>
       </c>
       <c r="S61" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="T61" t="inlineStr">
         <is>
@@ -7562,12 +6651,12 @@
       </c>
       <c r="Y61" t="inlineStr">
         <is>
-          <t>2024-08-22</t>
+          <t>2022-09-21</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
         <is>
-          <t>2024-08-22</t>
+          <t>2022-09-21</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7582,27 +6671,26 @@
       <c r="AT61" t="inlineStr"/>
       <c r="AW61" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Jennifer C. Johansson</t>
         </is>
       </c>
       <c r="AX61" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
-        </is>
-      </c>
-      <c r="AY61" t="inlineStr"/>
+          <t>Amanda Tas, Erland Lindblad, Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AY61" t="inlineStr">
+        <is>
+          <t>Naturvärdesinventering Y-län</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>119278908</v>
+        <v>119279051</v>
       </c>
       <c r="B62" t="n">
-        <v>57463</v>
-      </c>
-      <c r="C62" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91930</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7610,43 +6698,34 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>103021</v>
+        <v>5442</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I62" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="M62" t="inlineStr">
-        <is>
-          <t>stationär</t>
-        </is>
-      </c>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
           <t>Storstenbäcken, Storstenbäcken, Ång</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>598683</v>
+        <v>598610</v>
       </c>
       <c r="R62" t="n">
-        <v>7034343</v>
+        <v>7034505</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7676,19 +6755,9 @@
           <t>2024-08-22</t>
         </is>
       </c>
-      <c r="Z62" t="inlineStr">
-        <is>
-          <t>15:36</t>
-        </is>
-      </c>
       <c r="AA62" t="inlineStr">
         <is>
           <t>2024-08-22</t>
-        </is>
-      </c>
-      <c r="AB62" t="inlineStr">
-        <is>
-          <t>15:36</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7703,65 +6772,60 @@
       <c r="AT62" t="inlineStr"/>
       <c r="AW62" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX62" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>119279008</v>
+        <v>105162650</v>
       </c>
       <c r="B63" t="n">
-        <v>57310</v>
-      </c>
-      <c r="C63" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91872</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>100109</v>
+        <v>5447</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
-          <t>Storstenbäcken, Storstenbäcken, Ång</t>
+          <t>Norrtannflo värdetrakt, Ång</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>598744</v>
+        <v>598683</v>
       </c>
       <c r="R63" t="n">
-        <v>7034453</v>
+        <v>7034560</v>
       </c>
       <c r="S63" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T63" t="inlineStr">
         <is>
@@ -7785,27 +6849,12 @@
       </c>
       <c r="Y63" t="inlineStr">
         <is>
-          <t>2024-08-22</t>
-        </is>
-      </c>
-      <c r="Z63" t="inlineStr">
-        <is>
-          <t>15:48</t>
+          <t>2022-09-21</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
         <is>
-          <t>2024-08-22</t>
-        </is>
-      </c>
-      <c r="AB63" t="inlineStr">
-        <is>
-          <t>15:48</t>
-        </is>
-      </c>
-      <c r="AC63" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
+          <t>2022-09-21</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7820,65 +6869,64 @@
       <c r="AT63" t="inlineStr"/>
       <c r="AW63" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Jennifer C. Johansson</t>
         </is>
       </c>
       <c r="AX63" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
-        </is>
-      </c>
-      <c r="AY63" t="inlineStr"/>
+          <t>Amanda Tas, Erland Lindblad, Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AY63" t="inlineStr">
+        <is>
+          <t>Naturvärdesinventering Y-län</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>119280145</v>
+        <v>105162683</v>
       </c>
       <c r="B64" t="n">
-        <v>57310</v>
-      </c>
-      <c r="C64" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91872</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>100109</v>
+        <v>5447</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
-          <t>Storstenbäcken, Storstenbäcken, Ång</t>
+          <t>Norrtannflo värdetrakt, Ång</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>598349</v>
+        <v>598433</v>
       </c>
       <c r="R64" t="n">
-        <v>7034259</v>
+        <v>7034255</v>
       </c>
       <c r="S64" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T64" t="inlineStr">
         <is>
@@ -7902,27 +6950,12 @@
       </c>
       <c r="Y64" t="inlineStr">
         <is>
-          <t>2024-08-22</t>
-        </is>
-      </c>
-      <c r="Z64" t="inlineStr">
-        <is>
-          <t>16:52</t>
+          <t>2022-09-21</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
         <is>
-          <t>2024-08-22</t>
-        </is>
-      </c>
-      <c r="AB64" t="inlineStr">
-        <is>
-          <t>16:52</t>
-        </is>
-      </c>
-      <c r="AC64" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
+          <t>2022-09-21</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7937,65 +6970,64 @@
       <c r="AT64" t="inlineStr"/>
       <c r="AW64" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Jennifer C. Johansson</t>
         </is>
       </c>
       <c r="AX64" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
-        </is>
-      </c>
-      <c r="AY64" t="inlineStr"/>
+          <t>Amanda Tas, Erland Lindblad, Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AY64" t="inlineStr">
+        <is>
+          <t>Naturvärdesinventering Y-län</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>119280135</v>
+        <v>105162685</v>
       </c>
       <c r="B65" t="n">
-        <v>90562</v>
-      </c>
-      <c r="C65" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91872</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>1202</v>
+        <v>5447</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
-          <t>Storstenbäcken, Storstenbäcken, Ång</t>
+          <t>Norrtannflo värdetrakt, Ång</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>598365</v>
+        <v>598425</v>
       </c>
       <c r="R65" t="n">
-        <v>7034248</v>
+        <v>7034263</v>
       </c>
       <c r="S65" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T65" t="inlineStr">
         <is>
@@ -8019,12 +7051,12 @@
       </c>
       <c r="Y65" t="inlineStr">
         <is>
-          <t>2024-08-22</t>
+          <t>2022-09-21</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
         <is>
-          <t>2024-08-22</t>
+          <t>2022-09-21</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -8039,49 +7071,48 @@
       <c r="AT65" t="inlineStr"/>
       <c r="AW65" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Jennifer C. Johansson</t>
         </is>
       </c>
       <c r="AX65" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
-        </is>
-      </c>
-      <c r="AY65" t="inlineStr"/>
+          <t>Amanda Tas, Erland Lindblad, Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AY65" t="inlineStr">
+        <is>
+          <t>Naturvärdesinventering Y-län</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>119279051</v>
+        <v>119279605</v>
       </c>
       <c r="B66" t="n">
-        <v>90582</v>
-      </c>
-      <c r="C66" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91872</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>5442</v>
+        <v>5447</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -8091,10 +7122,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>598610</v>
+        <v>598616</v>
       </c>
       <c r="R66" t="n">
-        <v>7034505</v>
+        <v>7034570</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -8153,15 +7184,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>119279649</v>
+        <v>105162684</v>
       </c>
       <c r="B67" t="n">
-        <v>57310</v>
-      </c>
-      <c r="C67" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92556</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -8169,37 +7195,37 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>100109</v>
+        <v>5454</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Hornvaxskinn</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Crustoderma corneum</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Bourdot &amp; Galzin) Nakasone</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
       <c r="P67" t="inlineStr">
         <is>
-          <t>Storstenbäcken, Storstenbäcken, Ång</t>
+          <t>Norrtannflo värdetrakt, Ång</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>598612</v>
+        <v>598428</v>
       </c>
       <c r="R67" t="n">
-        <v>7034546</v>
+        <v>7034265</v>
       </c>
       <c r="S67" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T67" t="inlineStr">
         <is>
@@ -8223,27 +7249,12 @@
       </c>
       <c r="Y67" t="inlineStr">
         <is>
-          <t>2024-08-22</t>
-        </is>
-      </c>
-      <c r="Z67" t="inlineStr">
-        <is>
-          <t>16:26</t>
+          <t>2022-09-21</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
         <is>
-          <t>2024-08-22</t>
-        </is>
-      </c>
-      <c r="AB67" t="inlineStr">
-        <is>
-          <t>16:26</t>
-        </is>
-      </c>
-      <c r="AC67" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
+          <t>2022-09-21</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -8258,65 +7269,64 @@
       <c r="AT67" t="inlineStr"/>
       <c r="AW67" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Jennifer C. Johansson</t>
         </is>
       </c>
       <c r="AX67" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
-        </is>
-      </c>
-      <c r="AY67" t="inlineStr"/>
+          <t>Amanda Tas, Erland Lindblad, Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AY67" t="inlineStr">
+        <is>
+          <t>Naturvärdesinventering Y-län</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>119278756</v>
+        <v>105162639</v>
       </c>
       <c r="B68" t="n">
-        <v>90846</v>
-      </c>
-      <c r="C68" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>658</v>
+        <v>6425</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
-          <t>Storstenbäcken, Storstenbäcken, Ång</t>
+          <t>Norrtannflo värdetrakt, Ång</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>598485</v>
+        <v>598528</v>
       </c>
       <c r="R68" t="n">
-        <v>7034367</v>
+        <v>7034391</v>
       </c>
       <c r="S68" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T68" t="inlineStr">
         <is>
@@ -8340,12 +7350,12 @@
       </c>
       <c r="Y68" t="inlineStr">
         <is>
-          <t>2024-08-22</t>
+          <t>2022-09-21</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
         <is>
-          <t>2024-08-22</t>
+          <t>2022-09-21</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -8360,65 +7370,64 @@
       <c r="AT68" t="inlineStr"/>
       <c r="AW68" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Jennifer C. Johansson</t>
         </is>
       </c>
       <c r="AX68" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
-        </is>
-      </c>
-      <c r="AY68" t="inlineStr"/>
+          <t>Amanda Tas, Erland Lindblad, Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AY68" t="inlineStr">
+        <is>
+          <t>Naturvärdesinventering Y-län</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>119278599</v>
+        <v>105162642</v>
       </c>
       <c r="B69" t="n">
-        <v>90846</v>
-      </c>
-      <c r="C69" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>658</v>
+        <v>6425</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
-          <t>Storstenbäcken, Storstenbäcken, Ång</t>
+          <t>Norrtannflo värdetrakt, Ång</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>598483</v>
+        <v>598633</v>
       </c>
       <c r="R69" t="n">
-        <v>7034339</v>
+        <v>7034623</v>
       </c>
       <c r="S69" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T69" t="inlineStr">
         <is>
@@ -8442,12 +7451,12 @@
       </c>
       <c r="Y69" t="inlineStr">
         <is>
-          <t>2024-08-22</t>
+          <t>2022-09-21</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
         <is>
-          <t>2024-08-22</t>
+          <t>2022-09-21</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -8462,65 +7471,64 @@
       <c r="AT69" t="inlineStr"/>
       <c r="AW69" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Jennifer C. Johansson</t>
         </is>
       </c>
       <c r="AX69" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
-        </is>
-      </c>
-      <c r="AY69" t="inlineStr"/>
+          <t>Amanda Tas, Erland Lindblad, Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AY69" t="inlineStr">
+        <is>
+          <t>Naturvärdesinventering Y-län</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>119278432</v>
+        <v>105162647</v>
       </c>
       <c r="B70" t="n">
-        <v>90846</v>
-      </c>
-      <c r="C70" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>658</v>
+        <v>6425</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
-          <t>Storstenbäcken, Storstenbäcken, Ång</t>
+          <t>Norrtannflo värdetrakt, Ång</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>598410</v>
+        <v>598684</v>
       </c>
       <c r="R70" t="n">
-        <v>7034317</v>
+        <v>7034583</v>
       </c>
       <c r="S70" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T70" t="inlineStr">
         <is>
@@ -8544,12 +7552,12 @@
       </c>
       <c r="Y70" t="inlineStr">
         <is>
-          <t>2024-08-22</t>
+          <t>2022-09-21</t>
         </is>
       </c>
       <c r="AA70" t="inlineStr">
         <is>
-          <t>2024-08-22</t>
+          <t>2022-09-21</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -8564,70 +7572,64 @@
       <c r="AT70" t="inlineStr"/>
       <c r="AW70" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Jennifer C. Johansson</t>
         </is>
       </c>
       <c r="AX70" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
-        </is>
-      </c>
-      <c r="AY70" t="inlineStr"/>
+          <t>Amanda Tas, Erland Lindblad, Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AY70" t="inlineStr">
+        <is>
+          <t>Naturvärdesinventering Y-län</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>119278224</v>
+        <v>105162653</v>
       </c>
       <c r="B71" t="n">
-        <v>57310</v>
-      </c>
-      <c r="C71" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
-      <c r="M71" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P71" t="inlineStr">
         <is>
-          <t>Storstenbäcken, Storstenbäcken, Ång</t>
+          <t>Norrtannflo värdetrakt, Ång</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>598498</v>
+        <v>598665</v>
       </c>
       <c r="R71" t="n">
-        <v>7034222</v>
+        <v>7034542</v>
       </c>
       <c r="S71" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T71" t="inlineStr">
         <is>
@@ -8651,22 +7653,12 @@
       </c>
       <c r="Y71" t="inlineStr">
         <is>
-          <t>2024-08-22</t>
-        </is>
-      </c>
-      <c r="Z71" t="inlineStr">
-        <is>
-          <t>14:58</t>
+          <t>2022-09-21</t>
         </is>
       </c>
       <c r="AA71" t="inlineStr">
         <is>
-          <t>2024-08-22</t>
-        </is>
-      </c>
-      <c r="AB71" t="inlineStr">
-        <is>
-          <t>14:58</t>
+          <t>2022-09-21</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -8681,65 +7673,64 @@
       <c r="AT71" t="inlineStr"/>
       <c r="AW71" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Jennifer C. Johansson</t>
         </is>
       </c>
       <c r="AX71" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
-        </is>
-      </c>
-      <c r="AY71" t="inlineStr"/>
+          <t>Amanda Tas, Erland Lindblad, Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AY71" t="inlineStr">
+        <is>
+          <t>Naturvärdesinventering Y-län</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>119278487</v>
+        <v>105162657</v>
       </c>
       <c r="B72" t="n">
-        <v>90846</v>
-      </c>
-      <c r="C72" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>658</v>
+        <v>6425</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
       <c r="P72" t="inlineStr">
         <is>
-          <t>Storstenbäcken, Storstenbäcken, Ång</t>
+          <t>Norrtannflo värdetrakt, Ång</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>598580</v>
+        <v>598596</v>
       </c>
       <c r="R72" t="n">
-        <v>7034264</v>
+        <v>7034301</v>
       </c>
       <c r="S72" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T72" t="inlineStr">
         <is>
@@ -8763,22 +7754,12 @@
       </c>
       <c r="Y72" t="inlineStr">
         <is>
-          <t>2024-08-22</t>
-        </is>
-      </c>
-      <c r="Z72" t="inlineStr">
-        <is>
-          <t>15:16</t>
+          <t>2022-09-21</t>
         </is>
       </c>
       <c r="AA72" t="inlineStr">
         <is>
-          <t>2024-08-22</t>
-        </is>
-      </c>
-      <c r="AB72" t="inlineStr">
-        <is>
-          <t>15:16</t>
+          <t>2022-09-21</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -8793,70 +7774,64 @@
       <c r="AT72" t="inlineStr"/>
       <c r="AW72" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Jennifer C. Johansson</t>
         </is>
       </c>
       <c r="AX72" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
-        </is>
-      </c>
-      <c r="AY72" t="inlineStr"/>
+          <t>Amanda Tas, Erland Lindblad, Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AY72" t="inlineStr">
+        <is>
+          <t>Naturvärdesinventering Y-län</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>119278270</v>
+        <v>119278842</v>
       </c>
       <c r="B73" t="n">
-        <v>57310</v>
-      </c>
-      <c r="C73" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
-      <c r="M73" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P73" t="inlineStr">
         <is>
           <t>Storstenbäcken, Storstenbäcken, Ång</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>598520</v>
+        <v>598487</v>
       </c>
       <c r="R73" t="n">
-        <v>7034227</v>
+        <v>7034370</v>
       </c>
       <c r="S73" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T73" t="inlineStr">
         <is>
@@ -8883,19 +7858,9 @@
           <t>2024-08-22</t>
         </is>
       </c>
-      <c r="Z73" t="inlineStr">
-        <is>
-          <t>15:02</t>
-        </is>
-      </c>
       <c r="AA73" t="inlineStr">
         <is>
           <t>2024-08-22</t>
-        </is>
-      </c>
-      <c r="AB73" t="inlineStr">
-        <is>
-          <t>15:02</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -8910,69 +7875,60 @@
       <c r="AT73" t="inlineStr"/>
       <c r="AW73" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX73" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>119278422</v>
+        <v>105162661</v>
       </c>
       <c r="B74" t="n">
-        <v>97907</v>
-      </c>
-      <c r="C74" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79084</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>220787</v>
+        <v>6446</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I74" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr"/>
       <c r="P74" t="inlineStr">
         <is>
-          <t>Storstenbäcken, Storstenbäcken, Ång</t>
+          <t>Norrtannflo värdetrakt, Ång</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>598537</v>
+        <v>598565</v>
       </c>
       <c r="R74" t="n">
-        <v>7034202</v>
+        <v>7034299</v>
       </c>
       <c r="S74" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T74" t="inlineStr">
         <is>
@@ -8996,22 +7952,12 @@
       </c>
       <c r="Y74" t="inlineStr">
         <is>
-          <t>2024-08-22</t>
-        </is>
-      </c>
-      <c r="Z74" t="inlineStr">
-        <is>
-          <t>15:06</t>
+          <t>2022-09-21</t>
         </is>
       </c>
       <c r="AA74" t="inlineStr">
         <is>
-          <t>2024-08-22</t>
-        </is>
-      </c>
-      <c r="AB74" t="inlineStr">
-        <is>
-          <t>15:06</t>
+          <t>2022-09-21</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -9026,27 +7972,26 @@
       <c r="AT74" t="inlineStr"/>
       <c r="AW74" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Jennifer C. Johansson</t>
         </is>
       </c>
       <c r="AX74" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
-        </is>
-      </c>
-      <c r="AY74" t="inlineStr"/>
+          <t>Amanda Tas, Erland Lindblad, Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AY74" t="inlineStr">
+        <is>
+          <t>Naturvärdesinventering Y-län</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>119279160</v>
+        <v>105162662</v>
       </c>
       <c r="B75" t="n">
-        <v>90562</v>
-      </c>
-      <c r="C75" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79946</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -9054,37 +7999,37 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>1202</v>
+        <v>6453</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
       <c r="P75" t="inlineStr">
         <is>
-          <t>Storstenbäcken, Storstenbäcken, Ång</t>
+          <t>Norrtannflo värdetrakt, Ång</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>598621</v>
+        <v>598565</v>
       </c>
       <c r="R75" t="n">
-        <v>7034555</v>
+        <v>7034299</v>
       </c>
       <c r="S75" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T75" t="inlineStr">
         <is>
@@ -9108,12 +8053,12 @@
       </c>
       <c r="Y75" t="inlineStr">
         <is>
-          <t>2024-08-22</t>
+          <t>2022-09-21</t>
         </is>
       </c>
       <c r="AA75" t="inlineStr">
         <is>
-          <t>2024-08-22</t>
+          <t>2022-09-21</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -9128,27 +8073,26 @@
       <c r="AT75" t="inlineStr"/>
       <c r="AW75" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Jennifer C. Johansson</t>
         </is>
       </c>
       <c r="AX75" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
-        </is>
-      </c>
-      <c r="AY75" t="inlineStr"/>
+          <t>Amanda Tas, Erland Lindblad, Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AY75" t="inlineStr">
+        <is>
+          <t>Naturvärdesinventering Y-län</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>119279605</v>
+        <v>105162667</v>
       </c>
       <c r="B76" t="n">
-        <v>90527</v>
-      </c>
-      <c r="C76" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80336</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -9156,37 +8100,37 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>5447</v>
+        <v>6456</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
       <c r="P76" t="inlineStr">
         <is>
-          <t>Storstenbäcken, Storstenbäcken, Ång</t>
+          <t>Norrtannflo värdetrakt, Ång</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>598616</v>
+        <v>598537</v>
       </c>
       <c r="R76" t="n">
-        <v>7034570</v>
+        <v>7034307</v>
       </c>
       <c r="S76" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T76" t="inlineStr">
         <is>
@@ -9210,12 +8154,12 @@
       </c>
       <c r="Y76" t="inlineStr">
         <is>
-          <t>2024-08-22</t>
+          <t>2022-09-21</t>
         </is>
       </c>
       <c r="AA76" t="inlineStr">
         <is>
-          <t>2024-08-22</t>
+          <t>2022-09-21</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -9230,27 +8174,26 @@
       <c r="AT76" t="inlineStr"/>
       <c r="AW76" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Jennifer C. Johansson</t>
         </is>
       </c>
       <c r="AX76" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
-        </is>
-      </c>
-      <c r="AY76" t="inlineStr"/>
+          <t>Amanda Tas, Erland Lindblad, Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AY76" t="inlineStr">
+        <is>
+          <t>Naturvärdesinventering Y-län</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>119278413</v>
+        <v>105162645</v>
       </c>
       <c r="B77" t="n">
-        <v>90846</v>
-      </c>
-      <c r="C77" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -9258,37 +8201,37 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>658</v>
+        <v>6458</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
       <c r="P77" t="inlineStr">
         <is>
-          <t>Storstenbäcken, Storstenbäcken, Ång</t>
+          <t>Norrtannflo värdetrakt, Ång</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>598404</v>
+        <v>598689</v>
       </c>
       <c r="R77" t="n">
-        <v>7034323</v>
+        <v>7034595</v>
       </c>
       <c r="S77" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T77" t="inlineStr">
         <is>
@@ -9312,12 +8255,17 @@
       </c>
       <c r="Y77" t="inlineStr">
         <is>
-          <t>2024-08-22</t>
+          <t>2022-09-21</t>
         </is>
       </c>
       <c r="AA77" t="inlineStr">
         <is>
-          <t>2024-08-22</t>
+          <t>2022-09-21</t>
+        </is>
+      </c>
+      <c r="AC77" t="inlineStr">
+        <is>
+          <t>På gammal björk</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -9332,27 +8280,26 @@
       <c r="AT77" t="inlineStr"/>
       <c r="AW77" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Jennifer C. Johansson</t>
         </is>
       </c>
       <c r="AX77" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
-        </is>
-      </c>
-      <c r="AY77" t="inlineStr"/>
+          <t>Amanda Tas, Erland Lindblad, Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AY77" t="inlineStr">
+        <is>
+          <t>Naturvärdesinventering Y-län</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>119278420</v>
+        <v>105162655</v>
       </c>
       <c r="B78" t="n">
-        <v>90846</v>
-      </c>
-      <c r="C78" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -9360,37 +8307,37 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>658</v>
+        <v>6458</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
       <c r="P78" t="inlineStr">
         <is>
-          <t>Storstenbäcken, Storstenbäcken, Ång</t>
+          <t>Norrtannflo värdetrakt, Ång</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>598415</v>
+        <v>598668</v>
       </c>
       <c r="R78" t="n">
-        <v>7034330</v>
+        <v>7034492</v>
       </c>
       <c r="S78" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T78" t="inlineStr">
         <is>
@@ -9414,12 +8361,12 @@
       </c>
       <c r="Y78" t="inlineStr">
         <is>
-          <t>2024-08-22</t>
+          <t>2022-09-21</t>
         </is>
       </c>
       <c r="AA78" t="inlineStr">
         <is>
-          <t>2024-08-22</t>
+          <t>2022-09-21</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -9434,27 +8381,26 @@
       <c r="AT78" t="inlineStr"/>
       <c r="AW78" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Jennifer C. Johansson</t>
         </is>
       </c>
       <c r="AX78" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
-        </is>
-      </c>
-      <c r="AY78" t="inlineStr"/>
+          <t>Amanda Tas, Erland Lindblad, Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AY78" t="inlineStr">
+        <is>
+          <t>Naturvärdesinventering Y-län</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>119279166</v>
+        <v>106564418</v>
       </c>
       <c r="B79" t="n">
-        <v>56514</v>
-      </c>
-      <c r="C79" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -9462,39 +8408,37 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>102612</v>
+        <v>6458</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
-      <c r="M79" t="inlineStr">
-        <is>
-          <t>stationär</t>
-        </is>
-      </c>
+      <c r="J79" t="inlineStr"/>
+      <c r="K79" t="inlineStr"/>
+      <c r="N79" t="inlineStr"/>
       <c r="P79" t="inlineStr">
         <is>
-          <t>Storstenbäcken, Storstenbäcken, Ång</t>
+          <t>Blåbärshällarna, Ång</t>
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>598836</v>
+        <v>598668</v>
       </c>
       <c r="R79" t="n">
-        <v>7034550</v>
+        <v>7034494</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -9521,22 +8465,12 @@
       </c>
       <c r="Y79" t="inlineStr">
         <is>
-          <t>2024-08-22</t>
-        </is>
-      </c>
-      <c r="Z79" t="inlineStr">
-        <is>
-          <t>16:00</t>
+          <t>2023-02-09</t>
         </is>
       </c>
       <c r="AA79" t="inlineStr">
         <is>
-          <t>2024-08-22</t>
-        </is>
-      </c>
-      <c r="AB79" t="inlineStr">
-        <is>
-          <t>16:00</t>
+          <t>2023-02-09</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -9545,33 +8479,44 @@
       <c r="AE79" t="b">
         <v>0</v>
       </c>
+      <c r="AF79" t="inlineStr"/>
       <c r="AG79" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ79" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AK79" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AO79" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
       </c>
       <c r="AT79" t="inlineStr"/>
       <c r="AW79" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX79" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>119278912</v>
+        <v>105162638</v>
       </c>
       <c r="B80" t="n">
-        <v>57310</v>
-      </c>
-      <c r="C80" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9597,19 +8542,23 @@
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
+      <c r="K80" t="inlineStr"/>
+      <c r="L80" t="inlineStr"/>
+      <c r="M80" t="inlineStr"/>
+      <c r="N80" t="inlineStr"/>
       <c r="P80" t="inlineStr">
         <is>
-          <t>Storstenbäcken, Storstenbäcken, Ång</t>
+          <t>Norrtannflo värdetrakt, Ång</t>
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>598484</v>
+        <v>598399</v>
       </c>
       <c r="R80" t="n">
-        <v>7034390</v>
+        <v>7034300</v>
       </c>
       <c r="S80" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T80" t="inlineStr">
         <is>
@@ -9633,17 +8582,12 @@
       </c>
       <c r="Y80" t="inlineStr">
         <is>
-          <t>2024-08-22</t>
+          <t>2022-09-21</t>
         </is>
       </c>
       <c r="AA80" t="inlineStr">
         <is>
-          <t>2024-08-22</t>
-        </is>
-      </c>
-      <c r="AC80" t="inlineStr">
-        <is>
-          <t>Ringhack på gammal tall</t>
+          <t>2022-09-21</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -9658,27 +8602,26 @@
       <c r="AT80" t="inlineStr"/>
       <c r="AW80" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Jennifer C. Johansson</t>
         </is>
       </c>
       <c r="AX80" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
-        </is>
-      </c>
-      <c r="AY80" t="inlineStr"/>
+          <t>Amanda Tas, Erland Lindblad, Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AY80" t="inlineStr">
+        <is>
+          <t>Naturvärdesinventering Y-län</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>119279131</v>
+        <v>106564406</v>
       </c>
       <c r="B81" t="n">
-        <v>90846</v>
-      </c>
-      <c r="C81" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9686,37 +8629,45 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>658</v>
+        <v>100109</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
+      <c r="K81" t="inlineStr"/>
+      <c r="L81" t="inlineStr"/>
+      <c r="M81" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N81" t="inlineStr"/>
       <c r="P81" t="inlineStr">
         <is>
-          <t>Storstenbäcken, Storstenbäcken, Ång</t>
+          <t>Blåbärshällarna, Ång</t>
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>598616</v>
+        <v>598396</v>
       </c>
       <c r="R81" t="n">
-        <v>7034552</v>
+        <v>7034342</v>
       </c>
       <c r="S81" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T81" t="inlineStr">
         <is>
@@ -9740,12 +8691,22 @@
       </c>
       <c r="Y81" t="inlineStr">
         <is>
-          <t>2024-08-22</t>
+          <t>2023-02-09</t>
+        </is>
+      </c>
+      <c r="Z81" t="inlineStr">
+        <is>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AA81" t="inlineStr">
         <is>
-          <t>2024-08-22</t>
+          <t>2023-02-09</t>
+        </is>
+      </c>
+      <c r="AB81" t="inlineStr">
+        <is>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -9760,27 +8721,22 @@
       <c r="AT81" t="inlineStr"/>
       <c r="AW81" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX81" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>119278576</v>
+        <v>119278224</v>
       </c>
       <c r="B82" t="n">
-        <v>90846</v>
-      </c>
-      <c r="C82" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9788,37 +8744,42 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>658</v>
+        <v>100109</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
+      <c r="M82" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P82" t="inlineStr">
         <is>
           <t>Storstenbäcken, Storstenbäcken, Ång</t>
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>598475</v>
+        <v>598498</v>
       </c>
       <c r="R82" t="n">
-        <v>7034340</v>
+        <v>7034222</v>
       </c>
       <c r="S82" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T82" t="inlineStr">
         <is>
@@ -9845,9 +8806,19 @@
           <t>2024-08-22</t>
         </is>
       </c>
+      <c r="Z82" t="inlineStr">
+        <is>
+          <t>14:58</t>
+        </is>
+      </c>
       <c r="AA82" t="inlineStr">
         <is>
           <t>2024-08-22</t>
+        </is>
+      </c>
+      <c r="AB82" t="inlineStr">
+        <is>
+          <t>14:58</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -9862,27 +8833,22 @@
       <c r="AT82" t="inlineStr"/>
       <c r="AW82" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX82" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>119278406</v>
+        <v>119278270</v>
       </c>
       <c r="B83" t="n">
-        <v>90846</v>
-      </c>
-      <c r="C83" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9890,24 +8856,29 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>658</v>
+        <v>100109</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
+      <c r="M83" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P83" t="inlineStr">
         <is>
           <t>Storstenbäcken, Storstenbäcken, Ång</t>
@@ -9917,7 +8888,7 @@
         <v>598520</v>
       </c>
       <c r="R83" t="n">
-        <v>7034228</v>
+        <v>7034227</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -9949,7 +8920,7 @@
       </c>
       <c r="Z83" t="inlineStr">
         <is>
-          <t>15:04</t>
+          <t>15:02</t>
         </is>
       </c>
       <c r="AA83" t="inlineStr">
@@ -9959,7 +8930,7 @@
       </c>
       <c r="AB83" t="inlineStr">
         <is>
-          <t>15:04</t>
+          <t>15:02</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -9986,15 +8957,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>119278466</v>
+        <v>119278912</v>
       </c>
       <c r="B84" t="n">
-        <v>90846</v>
-      </c>
-      <c r="C84" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -10002,21 +8968,21 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>658</v>
+        <v>100109</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
@@ -10026,10 +8992,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>598446</v>
+        <v>598484</v>
       </c>
       <c r="R84" t="n">
-        <v>7034308</v>
+        <v>7034390</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -10062,6 +9028,11 @@
       <c r="AA84" t="inlineStr">
         <is>
           <t>2024-08-22</t>
+        </is>
+      </c>
+      <c r="AC84" t="inlineStr">
+        <is>
+          <t>Ringhack på gammal tall</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -10091,12 +9062,7 @@
         <v>119278919</v>
       </c>
       <c r="B85" t="n">
-        <v>57310</v>
-      </c>
-      <c r="C85" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -10205,37 +9171,32 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>119278212</v>
+        <v>119278968</v>
       </c>
       <c r="B86" t="n">
-        <v>90752</v>
-      </c>
-      <c r="C86" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>48</v>
+        <v>100109</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Lappticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Amylocystis lapponica</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Romell) Bondartsev &amp; Singer</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
@@ -10245,10 +9206,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>598364</v>
+        <v>598747</v>
       </c>
       <c r="R86" t="n">
-        <v>7034253</v>
+        <v>7034393</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -10278,9 +9239,24 @@
           <t>2024-08-22</t>
         </is>
       </c>
+      <c r="Z86" t="inlineStr">
+        <is>
+          <t>15:44</t>
+        </is>
+      </c>
       <c r="AA86" t="inlineStr">
         <is>
           <t>2024-08-22</t>
+        </is>
+      </c>
+      <c r="AB86" t="inlineStr">
+        <is>
+          <t>15:44</t>
+        </is>
+      </c>
+      <c r="AC86" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD86" t="b">
@@ -10295,27 +9271,22 @@
       <c r="AT86" t="inlineStr"/>
       <c r="AW86" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX86" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>119278019</v>
+        <v>119279008</v>
       </c>
       <c r="B87" t="n">
-        <v>90562</v>
-      </c>
-      <c r="C87" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -10323,21 +9294,21 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
@@ -10347,10 +9318,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>598348</v>
+        <v>598744</v>
       </c>
       <c r="R87" t="n">
-        <v>7034205</v>
+        <v>7034453</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -10380,9 +9351,24 @@
           <t>2024-08-22</t>
         </is>
       </c>
+      <c r="Z87" t="inlineStr">
+        <is>
+          <t>15:48</t>
+        </is>
+      </c>
       <c r="AA87" t="inlineStr">
         <is>
           <t>2024-08-22</t>
+        </is>
+      </c>
+      <c r="AB87" t="inlineStr">
+        <is>
+          <t>15:48</t>
+        </is>
+      </c>
+      <c r="AC87" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD87" t="b">
@@ -10397,27 +9383,22 @@
       <c r="AT87" t="inlineStr"/>
       <c r="AW87" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX87" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY87" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>119278518</v>
+        <v>119279649</v>
       </c>
       <c r="B88" t="n">
-        <v>90846</v>
-      </c>
-      <c r="C88" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -10425,21 +9406,21 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>658</v>
+        <v>100109</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
@@ -10449,10 +9430,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>598471</v>
+        <v>598612</v>
       </c>
       <c r="R88" t="n">
-        <v>7034306</v>
+        <v>7034546</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -10482,9 +9463,24 @@
           <t>2024-08-22</t>
         </is>
       </c>
+      <c r="Z88" t="inlineStr">
+        <is>
+          <t>16:26</t>
+        </is>
+      </c>
       <c r="AA88" t="inlineStr">
         <is>
           <t>2024-08-22</t>
+        </is>
+      </c>
+      <c r="AB88" t="inlineStr">
+        <is>
+          <t>16:26</t>
+        </is>
+      </c>
+      <c r="AC88" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD88" t="b">
@@ -10499,76 +9495,57 @@
       <c r="AT88" t="inlineStr"/>
       <c r="AW88" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX88" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY88" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>119278675</v>
+        <v>119280106</v>
       </c>
       <c r="B89" t="n">
-        <v>56522</v>
-      </c>
-      <c r="C89" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E89" t="n">
-        <v>100138</v>
+        <v>100109</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I89" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="L89" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
-      <c r="M89" t="inlineStr">
-        <is>
-          <t>stationär</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I89" t="inlineStr"/>
       <c r="P89" t="inlineStr">
         <is>
           <t>Storstenbäcken, Storstenbäcken, Ång</t>
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>598584</v>
+        <v>598406</v>
       </c>
       <c r="R89" t="n">
-        <v>7034293</v>
+        <v>7034339</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -10600,7 +9577,7 @@
       </c>
       <c r="Z89" t="inlineStr">
         <is>
-          <t>15:25</t>
+          <t>16:44</t>
         </is>
       </c>
       <c r="AA89" t="inlineStr">
@@ -10610,7 +9587,12 @@
       </c>
       <c r="AB89" t="inlineStr">
         <is>
-          <t>15:25</t>
+          <t>16:44</t>
+        </is>
+      </c>
+      <c r="AC89" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD89" t="b">
@@ -10637,15 +9619,10 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>119278968</v>
+        <v>119280145</v>
       </c>
       <c r="B90" t="n">
-        <v>57310</v>
-      </c>
-      <c r="C90" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -10677,10 +9654,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>598747</v>
+        <v>598349</v>
       </c>
       <c r="R90" t="n">
-        <v>7034393</v>
+        <v>7034259</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -10712,7 +9689,7 @@
       </c>
       <c r="Z90" t="inlineStr">
         <is>
-          <t>15:44</t>
+          <t>16:52</t>
         </is>
       </c>
       <c r="AA90" t="inlineStr">
@@ -10722,7 +9699,7 @@
       </c>
       <c r="AB90" t="inlineStr">
         <is>
-          <t>15:44</t>
+          <t>16:52</t>
         </is>
       </c>
       <c r="AC90" t="inlineStr">
@@ -10754,15 +9731,10 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>119278034</v>
+        <v>119280150</v>
       </c>
       <c r="B91" t="n">
-        <v>90846</v>
-      </c>
-      <c r="C91" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -10770,21 +9742,21 @@
         </is>
       </c>
       <c r="E91" t="n">
-        <v>658</v>
+        <v>100109</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
@@ -10794,13 +9766,13 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>598358</v>
+        <v>598331</v>
       </c>
       <c r="R91" t="n">
-        <v>7034250</v>
+        <v>7034255</v>
       </c>
       <c r="S91" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T91" t="inlineStr">
         <is>
@@ -10827,9 +9799,24 @@
           <t>2024-08-22</t>
         </is>
       </c>
+      <c r="Z91" t="inlineStr">
+        <is>
+          <t>16:53</t>
+        </is>
+      </c>
       <c r="AA91" t="inlineStr">
         <is>
           <t>2024-08-22</t>
+        </is>
+      </c>
+      <c r="AB91" t="inlineStr">
+        <is>
+          <t>16:53</t>
+        </is>
+      </c>
+      <c r="AC91" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD91" t="b">
@@ -10844,62 +9831,71 @@
       <c r="AT91" t="inlineStr"/>
       <c r="AW91" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX91" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY91" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>119280106</v>
+        <v>119278675</v>
       </c>
       <c r="B92" t="n">
-        <v>57310</v>
-      </c>
-      <c r="C92" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57141</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E92" t="n">
-        <v>100109</v>
+        <v>100138</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I92" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I92" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L92" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="M92" t="inlineStr">
+        <is>
+          <t>stationär</t>
+        </is>
+      </c>
       <c r="P92" t="inlineStr">
         <is>
           <t>Storstenbäcken, Storstenbäcken, Ång</t>
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>598406</v>
+        <v>598584</v>
       </c>
       <c r="R92" t="n">
-        <v>7034339</v>
+        <v>7034293</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -10931,7 +9927,7 @@
       </c>
       <c r="Z92" t="inlineStr">
         <is>
-          <t>16:44</t>
+          <t>15:25</t>
         </is>
       </c>
       <c r="AA92" t="inlineStr">
@@ -10941,12 +9937,7 @@
       </c>
       <c r="AB92" t="inlineStr">
         <is>
-          <t>16:44</t>
-        </is>
-      </c>
-      <c r="AC92" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
+          <t>15:25</t>
         </is>
       </c>
       <c r="AD92" t="b">
@@ -10973,55 +9964,45 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>119279175</v>
+        <v>105162644</v>
       </c>
       <c r="B93" t="n">
-        <v>57463</v>
-      </c>
-      <c r="C93" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57132</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E93" t="n">
-        <v>103021</v>
+        <v>102612</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
-      <c r="M93" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="P93" t="inlineStr">
         <is>
-          <t>Storstenbäcken, Storstenbäcken, Ång</t>
+          <t>Norrtannflo värdetrakt, Ång</t>
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>598634</v>
+        <v>598679</v>
       </c>
       <c r="R93" t="n">
-        <v>7034559</v>
+        <v>7034596</v>
       </c>
       <c r="S93" t="n">
         <v>25</v>
@@ -11048,12 +10029,12 @@
       </c>
       <c r="Y93" t="inlineStr">
         <is>
-          <t>2024-08-22</t>
+          <t>2022-09-21</t>
         </is>
       </c>
       <c r="AA93" t="inlineStr">
         <is>
-          <t>2024-08-22</t>
+          <t>2022-09-21</t>
         </is>
       </c>
       <c r="AD93" t="b">
@@ -11068,54 +10049,54 @@
       <c r="AT93" t="inlineStr"/>
       <c r="AW93" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Jennifer C. Johansson</t>
         </is>
       </c>
       <c r="AX93" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
-        </is>
-      </c>
-      <c r="AY93" t="inlineStr"/>
+          <t>Amanda Tas, Erland Lindblad, Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AY93" t="inlineStr">
+        <is>
+          <t>Naturvärdesinventering Y-län</t>
+        </is>
+      </c>
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>119277960</v>
+        <v>119279166</v>
       </c>
       <c r="B94" t="n">
-        <v>97907</v>
-      </c>
-      <c r="C94" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57132</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E94" t="n">
-        <v>220787</v>
+        <v>102612</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I94" t="inlineStr">
-        <is>
-          <t>20</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I94" t="inlineStr"/>
+      <c r="M94" t="inlineStr">
+        <is>
+          <t>stationär</t>
         </is>
       </c>
       <c r="P94" t="inlineStr">
@@ -11124,10 +10105,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>598364</v>
+        <v>598836</v>
       </c>
       <c r="R94" t="n">
-        <v>7034215</v>
+        <v>7034550</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -11159,7 +10140,7 @@
       </c>
       <c r="Z94" t="inlineStr">
         <is>
-          <t>14:47</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="AA94" t="inlineStr">
@@ -11169,7 +10150,7 @@
       </c>
       <c r="AB94" t="inlineStr">
         <is>
-          <t>14:47</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="AD94" t="b">
@@ -11193,6 +10174,760 @@
         </is>
       </c>
       <c r="AY94" t="inlineStr"/>
+    </row>
+    <row r="95">
+      <c r="A95" t="n">
+        <v>105162637</v>
+      </c>
+      <c r="B95" t="n">
+        <v>58114</v>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E95" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H95" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I95" t="inlineStr"/>
+      <c r="P95" t="inlineStr">
+        <is>
+          <t>Norrtannflo värdetrakt, Ång</t>
+        </is>
+      </c>
+      <c r="Q95" t="n">
+        <v>598555</v>
+      </c>
+      <c r="R95" t="n">
+        <v>7034435</v>
+      </c>
+      <c r="S95" t="n">
+        <v>25</v>
+      </c>
+      <c r="T95" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U95" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V95" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W95" t="inlineStr">
+        <is>
+          <t>Ådals-Liden</t>
+        </is>
+      </c>
+      <c r="Y95" t="inlineStr">
+        <is>
+          <t>2022-09-21</t>
+        </is>
+      </c>
+      <c r="AA95" t="inlineStr">
+        <is>
+          <t>2022-09-21</t>
+        </is>
+      </c>
+      <c r="AD95" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE95" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG95" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT95" t="inlineStr"/>
+      <c r="AW95" t="inlineStr">
+        <is>
+          <t>Jennifer C. Johansson</t>
+        </is>
+      </c>
+      <c r="AX95" t="inlineStr">
+        <is>
+          <t>Amanda Tas, Erland Lindblad, Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AY95" t="inlineStr">
+        <is>
+          <t>Naturvärdesinventering Y-län</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="n">
+        <v>119278908</v>
+      </c>
+      <c r="B96" t="n">
+        <v>58114</v>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E96" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F96" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G96" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H96" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I96" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M96" t="inlineStr">
+        <is>
+          <t>stationär</t>
+        </is>
+      </c>
+      <c r="P96" t="inlineStr">
+        <is>
+          <t>Storstenbäcken, Storstenbäcken, Ång</t>
+        </is>
+      </c>
+      <c r="Q96" t="n">
+        <v>598683</v>
+      </c>
+      <c r="R96" t="n">
+        <v>7034343</v>
+      </c>
+      <c r="S96" t="n">
+        <v>10</v>
+      </c>
+      <c r="T96" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U96" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V96" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W96" t="inlineStr">
+        <is>
+          <t>Ådals-Liden</t>
+        </is>
+      </c>
+      <c r="Y96" t="inlineStr">
+        <is>
+          <t>2024-08-22</t>
+        </is>
+      </c>
+      <c r="Z96" t="inlineStr">
+        <is>
+          <t>15:36</t>
+        </is>
+      </c>
+      <c r="AA96" t="inlineStr">
+        <is>
+          <t>2024-08-22</t>
+        </is>
+      </c>
+      <c r="AB96" t="inlineStr">
+        <is>
+          <t>15:36</t>
+        </is>
+      </c>
+      <c r="AD96" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE96" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG96" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT96" t="inlineStr"/>
+      <c r="AW96" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AX96" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AY96" t="inlineStr"/>
+    </row>
+    <row r="97">
+      <c r="A97" t="n">
+        <v>119279175</v>
+      </c>
+      <c r="B97" t="n">
+        <v>58114</v>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E97" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F97" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G97" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H97" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I97" t="inlineStr"/>
+      <c r="M97" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="P97" t="inlineStr">
+        <is>
+          <t>Storstenbäcken, Storstenbäcken, Ång</t>
+        </is>
+      </c>
+      <c r="Q97" t="n">
+        <v>598634</v>
+      </c>
+      <c r="R97" t="n">
+        <v>7034559</v>
+      </c>
+      <c r="S97" t="n">
+        <v>25</v>
+      </c>
+      <c r="T97" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U97" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V97" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W97" t="inlineStr">
+        <is>
+          <t>Ådals-Liden</t>
+        </is>
+      </c>
+      <c r="Y97" t="inlineStr">
+        <is>
+          <t>2024-08-22</t>
+        </is>
+      </c>
+      <c r="AA97" t="inlineStr">
+        <is>
+          <t>2024-08-22</t>
+        </is>
+      </c>
+      <c r="AD97" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE97" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG97" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT97" t="inlineStr"/>
+      <c r="AW97" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX97" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY97" t="inlineStr"/>
+    </row>
+    <row r="98">
+      <c r="A98" t="n">
+        <v>119280121</v>
+      </c>
+      <c r="B98" t="n">
+        <v>58817</v>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E98" t="n">
+        <v>208249</v>
+      </c>
+      <c r="F98" t="inlineStr">
+        <is>
+          <t>Vanlig groda</t>
+        </is>
+      </c>
+      <c r="G98" t="inlineStr">
+        <is>
+          <t>Rana temporaria</t>
+        </is>
+      </c>
+      <c r="H98" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I98" t="inlineStr"/>
+      <c r="P98" t="inlineStr">
+        <is>
+          <t>Storstenbäcken, Storstenbäcken, Ång</t>
+        </is>
+      </c>
+      <c r="Q98" t="n">
+        <v>598391</v>
+      </c>
+      <c r="R98" t="n">
+        <v>7034279</v>
+      </c>
+      <c r="S98" t="n">
+        <v>10</v>
+      </c>
+      <c r="T98" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U98" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V98" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W98" t="inlineStr">
+        <is>
+          <t>Ådals-Liden</t>
+        </is>
+      </c>
+      <c r="Y98" t="inlineStr">
+        <is>
+          <t>2024-08-22</t>
+        </is>
+      </c>
+      <c r="Z98" t="inlineStr">
+        <is>
+          <t>16:47</t>
+        </is>
+      </c>
+      <c r="AA98" t="inlineStr">
+        <is>
+          <t>2024-08-22</t>
+        </is>
+      </c>
+      <c r="AB98" t="inlineStr">
+        <is>
+          <t>16:47</t>
+        </is>
+      </c>
+      <c r="AD98" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE98" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG98" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT98" t="inlineStr"/>
+      <c r="AW98" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AX98" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AY98" t="inlineStr"/>
+    </row>
+    <row r="99">
+      <c r="A99" t="n">
+        <v>105162687</v>
+      </c>
+      <c r="B99" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E99" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F99" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G99" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H99" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I99" t="inlineStr"/>
+      <c r="P99" t="inlineStr">
+        <is>
+          <t>Norrtannflo värdetrakt, Ång</t>
+        </is>
+      </c>
+      <c r="Q99" t="n">
+        <v>598365</v>
+      </c>
+      <c r="R99" t="n">
+        <v>7034225</v>
+      </c>
+      <c r="S99" t="n">
+        <v>25</v>
+      </c>
+      <c r="T99" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U99" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V99" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W99" t="inlineStr">
+        <is>
+          <t>Ådals-Liden</t>
+        </is>
+      </c>
+      <c r="Y99" t="inlineStr">
+        <is>
+          <t>2022-09-21</t>
+        </is>
+      </c>
+      <c r="AA99" t="inlineStr">
+        <is>
+          <t>2022-09-21</t>
+        </is>
+      </c>
+      <c r="AC99" t="inlineStr">
+        <is>
+          <t>Ett femtiotal</t>
+        </is>
+      </c>
+      <c r="AD99" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE99" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG99" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT99" t="inlineStr"/>
+      <c r="AW99" t="inlineStr">
+        <is>
+          <t>Jennifer C. Johansson</t>
+        </is>
+      </c>
+      <c r="AX99" t="inlineStr">
+        <is>
+          <t>Amanda Tas, Erland Lindblad, Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AY99" t="inlineStr">
+        <is>
+          <t>Naturvärdesinventering Y-län</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="n">
+        <v>119277960</v>
+      </c>
+      <c r="B100" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E100" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F100" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G100" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H100" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I100" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="P100" t="inlineStr">
+        <is>
+          <t>Storstenbäcken, Storstenbäcken, Ång</t>
+        </is>
+      </c>
+      <c r="Q100" t="n">
+        <v>598364</v>
+      </c>
+      <c r="R100" t="n">
+        <v>7034215</v>
+      </c>
+      <c r="S100" t="n">
+        <v>10</v>
+      </c>
+      <c r="T100" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U100" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V100" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W100" t="inlineStr">
+        <is>
+          <t>Ådals-Liden</t>
+        </is>
+      </c>
+      <c r="Y100" t="inlineStr">
+        <is>
+          <t>2024-08-22</t>
+        </is>
+      </c>
+      <c r="Z100" t="inlineStr">
+        <is>
+          <t>14:47</t>
+        </is>
+      </c>
+      <c r="AA100" t="inlineStr">
+        <is>
+          <t>2024-08-22</t>
+        </is>
+      </c>
+      <c r="AB100" t="inlineStr">
+        <is>
+          <t>14:47</t>
+        </is>
+      </c>
+      <c r="AD100" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE100" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG100" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT100" t="inlineStr"/>
+      <c r="AW100" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AX100" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AY100" t="inlineStr"/>
+    </row>
+    <row r="101">
+      <c r="A101" t="n">
+        <v>119278422</v>
+      </c>
+      <c r="B101" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E101" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F101" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G101" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H101" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I101" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="P101" t="inlineStr">
+        <is>
+          <t>Storstenbäcken, Storstenbäcken, Ång</t>
+        </is>
+      </c>
+      <c r="Q101" t="n">
+        <v>598537</v>
+      </c>
+      <c r="R101" t="n">
+        <v>7034202</v>
+      </c>
+      <c r="S101" t="n">
+        <v>10</v>
+      </c>
+      <c r="T101" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U101" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V101" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W101" t="inlineStr">
+        <is>
+          <t>Ådals-Liden</t>
+        </is>
+      </c>
+      <c r="Y101" t="inlineStr">
+        <is>
+          <t>2024-08-22</t>
+        </is>
+      </c>
+      <c r="Z101" t="inlineStr">
+        <is>
+          <t>15:06</t>
+        </is>
+      </c>
+      <c r="AA101" t="inlineStr">
+        <is>
+          <t>2024-08-22</t>
+        </is>
+      </c>
+      <c r="AB101" t="inlineStr">
+        <is>
+          <t>15:06</t>
+        </is>
+      </c>
+      <c r="AD101" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE101" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG101" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT101" t="inlineStr"/>
+      <c r="AW101" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AX101" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AY101" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 31322-2024 artfynd.xlsx
+++ b/artfynd/A 31322-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY101"/>
+  <dimension ref="A1:AZ101"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -773,6 +778,11 @@
           <t>Naturvärdesinventering Y-län</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105162651</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -870,6 +880,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119278212</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -971,6 +986,11 @@
           <t>Naturvärdesinventering Y-län</t>
         </is>
       </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105162682</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1072,6 +1092,11 @@
           <t>Naturvärdesinventering Y-län</t>
         </is>
       </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105162663</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1173,6 +1198,11 @@
           <t>Naturvärdesinventering Y-län</t>
         </is>
       </c>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105162679</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1274,6 +1304,11 @@
           <t>Naturvärdesinventering Y-län</t>
         </is>
       </c>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105162640</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1375,6 +1410,11 @@
           <t>Naturvärdesinventering Y-län</t>
         </is>
       </c>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105162641</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1476,6 +1516,11 @@
           <t>Naturvärdesinventering Y-län</t>
         </is>
       </c>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105162643</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1577,6 +1622,11 @@
           <t>Naturvärdesinventering Y-län</t>
         </is>
       </c>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105162649</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1678,6 +1728,11 @@
           <t>Naturvärdesinventering Y-län</t>
         </is>
       </c>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105162654</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1779,6 +1834,11 @@
           <t>Naturvärdesinventering Y-län</t>
         </is>
       </c>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105162658</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1880,6 +1940,11 @@
           <t>Naturvärdesinventering Y-län</t>
         </is>
       </c>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105162660</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1981,6 +2046,11 @@
           <t>Naturvärdesinventering Y-län</t>
         </is>
       </c>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105162664</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2082,6 +2152,11 @@
           <t>Naturvärdesinventering Y-län</t>
         </is>
       </c>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105162665</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2183,6 +2258,11 @@
           <t>Naturvärdesinventering Y-län</t>
         </is>
       </c>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105162668</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2282,6 +2362,11 @@
       <c r="AY17" t="inlineStr">
         <is>
           <t>Naturvärdesinventering Y-län</t>
+        </is>
+      </c>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105162669</t>
         </is>
       </c>
     </row>
@@ -2389,6 +2474,11 @@
           <t>Naturvärdesinventering Y-län</t>
         </is>
       </c>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105162671</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2490,6 +2580,11 @@
           <t>Naturvärdesinventering Y-län</t>
         </is>
       </c>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105162673</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2591,6 +2686,11 @@
           <t>Naturvärdesinventering Y-län</t>
         </is>
       </c>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105162675</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2688,6 +2788,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119277952</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2785,6 +2890,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119278034</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2892,6 +3002,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119278406</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -2989,6 +3104,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119278413</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3086,6 +3206,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119278420</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3183,6 +3308,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119278432</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3280,6 +3410,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119278466</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3387,6 +3522,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119278487</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3484,6 +3624,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119278518</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3581,6 +3726,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119278576</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3678,6 +3828,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119278599</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -3775,6 +3930,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119278693</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -3872,6 +4032,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119278756</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -3969,6 +4134,11 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119279131</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4066,6 +4236,11 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119280133</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4167,6 +4342,11 @@
           <t>Naturvärdesinventering Y-län</t>
         </is>
       </c>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105162646</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4268,6 +4448,11 @@
           <t>Naturvärdesinventering Y-län</t>
         </is>
       </c>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105162648</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -4369,6 +4554,11 @@
           <t>Naturvärdesinventering Y-län</t>
         </is>
       </c>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105162656</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -4468,6 +4658,11 @@
       <c r="AY39" t="inlineStr">
         <is>
           <t>Naturvärdesinventering Y-län</t>
+        </is>
+      </c>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105162680</t>
         </is>
       </c>
     </row>
@@ -4575,6 +4770,11 @@
           <t>Naturvärdesinventering Y-län</t>
         </is>
       </c>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105162686</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -4676,6 +4876,11 @@
           <t>Naturvärdesinventering Y-län</t>
         </is>
       </c>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105162688</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -4777,6 +4982,11 @@
           <t>Naturvärdesinventering Y-län</t>
         </is>
       </c>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105162689</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -4878,6 +5088,11 @@
           <t>Naturvärdesinventering Y-län</t>
         </is>
       </c>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105162690</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -4975,6 +5190,11 @@
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119277958</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -5072,6 +5292,11 @@
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119278019</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -5169,6 +5394,11 @@
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
+      <c r="AZ46" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119278582</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -5266,6 +5496,11 @@
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
+      <c r="AZ47" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119279160</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -5373,6 +5608,11 @@
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
+      <c r="AZ48" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119279180</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -5470,6 +5710,11 @@
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
+      <c r="AZ49" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119280135</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -5571,6 +5816,11 @@
           <t>Naturvärdesinventering Y-län</t>
         </is>
       </c>
+      <c r="AZ50" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105162666</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -5672,6 +5922,11 @@
           <t>Naturvärdesinventering Y-län</t>
         </is>
       </c>
+      <c r="AZ51" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105162659</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -5773,6 +6028,11 @@
           <t>Naturvärdesinventering Y-län</t>
         </is>
       </c>
+      <c r="AZ52" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105162674</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -5874,6 +6134,11 @@
           <t>Naturvärdesinventering Y-län</t>
         </is>
       </c>
+      <c r="AZ53" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105162678</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -5975,6 +6240,11 @@
           <t>Naturvärdesinventering Y-län</t>
         </is>
       </c>
+      <c r="AZ54" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105162652</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -6076,6 +6346,11 @@
           <t>Naturvärdesinventering Y-län</t>
         </is>
       </c>
+      <c r="AZ55" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105162672</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
@@ -6177,6 +6452,11 @@
           <t>Naturvärdesinventering Y-län</t>
         </is>
       </c>
+      <c r="AZ56" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105162676</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
@@ -6278,6 +6558,11 @@
           <t>Naturvärdesinventering Y-län</t>
         </is>
       </c>
+      <c r="AZ57" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105162677</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
@@ -6379,6 +6664,11 @@
           <t>Naturvärdesinventering Y-län</t>
         </is>
       </c>
+      <c r="AZ58" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105162681</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
@@ -6486,6 +6776,11 @@
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
+      <c r="AZ59" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119279419</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
@@ -6583,6 +6878,11 @@
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
+      <c r="AZ60" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119279544</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
@@ -6684,6 +6984,11 @@
           <t>Naturvärdesinventering Y-län</t>
         </is>
       </c>
+      <c r="AZ61" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105162670</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
@@ -6781,6 +7086,11 @@
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
+      <c r="AZ62" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119279051</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
@@ -6882,6 +7192,11 @@
           <t>Naturvärdesinventering Y-län</t>
         </is>
       </c>
+      <c r="AZ63" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105162650</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
@@ -6983,6 +7298,11 @@
           <t>Naturvärdesinventering Y-län</t>
         </is>
       </c>
+      <c r="AZ64" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105162683</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
@@ -7084,6 +7404,11 @@
           <t>Naturvärdesinventering Y-län</t>
         </is>
       </c>
+      <c r="AZ65" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105162685</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
@@ -7181,6 +7506,11 @@
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
+      <c r="AZ66" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119279605</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
@@ -7282,6 +7612,11 @@
           <t>Naturvärdesinventering Y-län</t>
         </is>
       </c>
+      <c r="AZ67" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105162684</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
@@ -7383,6 +7718,11 @@
           <t>Naturvärdesinventering Y-län</t>
         </is>
       </c>
+      <c r="AZ68" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105162639</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
@@ -7484,6 +7824,11 @@
           <t>Naturvärdesinventering Y-län</t>
         </is>
       </c>
+      <c r="AZ69" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105162642</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
@@ -7585,6 +7930,11 @@
           <t>Naturvärdesinventering Y-län</t>
         </is>
       </c>
+      <c r="AZ70" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105162647</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
@@ -7686,6 +8036,11 @@
           <t>Naturvärdesinventering Y-län</t>
         </is>
       </c>
+      <c r="AZ71" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105162653</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
@@ -7787,6 +8142,11 @@
           <t>Naturvärdesinventering Y-län</t>
         </is>
       </c>
+      <c r="AZ72" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105162657</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
@@ -7884,6 +8244,11 @@
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
+      <c r="AZ73" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119278842</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
@@ -7985,6 +8350,11 @@
           <t>Naturvärdesinventering Y-län</t>
         </is>
       </c>
+      <c r="AZ74" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105162661</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
@@ -8086,6 +8456,11 @@
           <t>Naturvärdesinventering Y-län</t>
         </is>
       </c>
+      <c r="AZ75" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105162662</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
@@ -8187,6 +8562,11 @@
           <t>Naturvärdesinventering Y-län</t>
         </is>
       </c>
+      <c r="AZ76" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105162667</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
@@ -8293,6 +8673,11 @@
           <t>Naturvärdesinventering Y-län</t>
         </is>
       </c>
+      <c r="AZ77" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105162645</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
@@ -8392,6 +8777,11 @@
       <c r="AY78" t="inlineStr">
         <is>
           <t>Naturvärdesinventering Y-län</t>
+        </is>
+      </c>
+      <c r="AZ78" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105162655</t>
         </is>
       </c>
     </row>
@@ -8510,6 +8900,11 @@
         </is>
       </c>
       <c r="AY79" t="inlineStr"/>
+      <c r="AZ79" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106564418</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="n">
@@ -8615,6 +9010,11 @@
           <t>Naturvärdesinventering Y-län</t>
         </is>
       </c>
+      <c r="AZ80" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105162638</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="n">
@@ -8730,6 +9130,11 @@
         </is>
       </c>
       <c r="AY81" t="inlineStr"/>
+      <c r="AZ81" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106564406</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="n">
@@ -8842,6 +9247,11 @@
         </is>
       </c>
       <c r="AY82" t="inlineStr"/>
+      <c r="AZ82" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119278224</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="n">
@@ -8954,6 +9364,11 @@
         </is>
       </c>
       <c r="AY83" t="inlineStr"/>
+      <c r="AZ83" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119278270</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="n">
@@ -9056,6 +9471,11 @@
         </is>
       </c>
       <c r="AY84" t="inlineStr"/>
+      <c r="AZ84" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119278912</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="n">
@@ -9168,6 +9588,11 @@
         </is>
       </c>
       <c r="AY85" t="inlineStr"/>
+      <c r="AZ85" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119278919</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="n">
@@ -9280,6 +9705,11 @@
         </is>
       </c>
       <c r="AY86" t="inlineStr"/>
+      <c r="AZ86" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119278968</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="n">
@@ -9392,6 +9822,11 @@
         </is>
       </c>
       <c r="AY87" t="inlineStr"/>
+      <c r="AZ87" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119279008</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="n">
@@ -9504,6 +9939,11 @@
         </is>
       </c>
       <c r="AY88" t="inlineStr"/>
+      <c r="AZ88" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119279649</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="n">
@@ -9616,6 +10056,11 @@
         </is>
       </c>
       <c r="AY89" t="inlineStr"/>
+      <c r="AZ89" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119280106</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="n">
@@ -9728,6 +10173,11 @@
         </is>
       </c>
       <c r="AY90" t="inlineStr"/>
+      <c r="AZ90" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119280145</t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="n">
@@ -9840,6 +10290,11 @@
         </is>
       </c>
       <c r="AY91" t="inlineStr"/>
+      <c r="AZ91" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119280150</t>
+        </is>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="n">
@@ -9961,6 +10416,11 @@
         </is>
       </c>
       <c r="AY92" t="inlineStr"/>
+      <c r="AZ92" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119278675</t>
+        </is>
+      </c>
     </row>
     <row r="93">
       <c r="A93" t="n">
@@ -10062,6 +10522,11 @@
           <t>Naturvärdesinventering Y-län</t>
         </is>
       </c>
+      <c r="AZ93" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105162644</t>
+        </is>
+      </c>
     </row>
     <row r="94">
       <c r="A94" t="n">
@@ -10174,6 +10639,11 @@
         </is>
       </c>
       <c r="AY94" t="inlineStr"/>
+      <c r="AZ94" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119279166</t>
+        </is>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="n">
@@ -10275,6 +10745,11 @@
           <t>Naturvärdesinventering Y-län</t>
         </is>
       </c>
+      <c r="AZ95" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105162637</t>
+        </is>
+      </c>
     </row>
     <row r="96">
       <c r="A96" t="n">
@@ -10391,6 +10866,11 @@
         </is>
       </c>
       <c r="AY96" t="inlineStr"/>
+      <c r="AZ96" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119278908</t>
+        </is>
+      </c>
     </row>
     <row r="97">
       <c r="A97" t="n">
@@ -10493,6 +10973,11 @@
         </is>
       </c>
       <c r="AY97" t="inlineStr"/>
+      <c r="AZ97" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119279175</t>
+        </is>
+      </c>
     </row>
     <row r="98">
       <c r="A98" t="n">
@@ -10600,6 +11085,11 @@
         </is>
       </c>
       <c r="AY98" t="inlineStr"/>
+      <c r="AZ98" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119280121</t>
+        </is>
+      </c>
     </row>
     <row r="99">
       <c r="A99" t="n">
@@ -10706,6 +11196,11 @@
           <t>Naturvärdesinventering Y-län</t>
         </is>
       </c>
+      <c r="AZ99" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105162687</t>
+        </is>
+      </c>
     </row>
     <row r="100">
       <c r="A100" t="n">
@@ -10817,6 +11312,11 @@
         </is>
       </c>
       <c r="AY100" t="inlineStr"/>
+      <c r="AZ100" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119277960</t>
+        </is>
+      </c>
     </row>
     <row r="101">
       <c r="A101" t="n">
@@ -10928,8 +11428,115 @@
         </is>
       </c>
       <c r="AY101" t="inlineStr"/>
+      <c r="AZ101" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119278422</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ49" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ50" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ51" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ52" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ53" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ54" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ55" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ56" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ57" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ58" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ59" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ60" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ61" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ62" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ63" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ64" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ65" r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ66" r:id="rId65"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ67" r:id="rId66"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ68" r:id="rId67"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ69" r:id="rId68"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ70" r:id="rId69"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ71" r:id="rId70"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ72" r:id="rId71"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ73" r:id="rId72"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ74" r:id="rId73"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ75" r:id="rId74"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ76" r:id="rId75"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ77" r:id="rId76"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ78" r:id="rId77"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ79" r:id="rId78"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ80" r:id="rId79"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ81" r:id="rId80"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ82" r:id="rId81"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ83" r:id="rId82"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ84" r:id="rId83"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ85" r:id="rId84"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ86" r:id="rId85"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ87" r:id="rId86"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ88" r:id="rId87"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ89" r:id="rId88"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ90" r:id="rId89"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ91" r:id="rId90"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ92" r:id="rId91"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ93" r:id="rId92"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ94" r:id="rId93"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ95" r:id="rId94"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ96" r:id="rId95"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ97" r:id="rId96"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ98" r:id="rId97"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ99" r:id="rId98"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ100" r:id="rId99"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ101" r:id="rId100"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>